--- a/umbrales_color_annexed_19-06-2026.xlsx
+++ b/umbrales_color_annexed_19-06-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDSN\Atlas2025\R_codes\Final\Output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\sdsn\atlas_sdsn_paolo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C7C9F6-8175-4BA3-92F4-8B7EE79631AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{444AFBA4-1E27-4959-83BC-C66D962AC11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,9 +601,6 @@
     <t>Cantidad de conflictos</t>
   </si>
   <si>
-    <t>Criterio de expertos con base en la Agenda 2030 para el Desarrollo Sostenible de ONU (Organización de las Naciones Unidas)</t>
-  </si>
-  <si>
     <t>16_09_01_04_nic</t>
   </si>
   <si>
@@ -623,6 +620,9 @@
   </si>
   <si>
     <t>Criterio de expertos (Taller externo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta 16.1 Reducir significativamente todas las formas de violencia y las correspondientes tasas de mortalidad en todo el mundo </t>
   </si>
 </sst>
 </file>
@@ -666,11 +666,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -979,6 +980,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="30.21875" customWidth="1"/>
+    <col min="12" max="12" width="7.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2217,22 +2219,22 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="H33">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="I33">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J33">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -3979,19 +3981,19 @@
       <c r="K79">
         <v>1000</v>
       </c>
-      <c r="L79" t="s">
-        <v>192</v>
+      <c r="L79" s="2" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B80">
         <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D80">
         <v>100</v>
@@ -4023,13 +4025,13 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B81">
         <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D81">
         <v>100</v>
@@ -4061,13 +4063,13 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B82">
         <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D82">
         <v>5000</v>
@@ -4094,10 +4096,11 @@
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/umbrales_color_annexed_19-06-2026.xlsx
+++ b/umbrales_color_annexed_19-06-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\sdsn\atlas_sdsn_paolo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{444AFBA4-1E27-4959-83BC-C66D962AC11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795D8703-4212-4910-911B-72E82F3B020B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,12 +666,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2210,7 +2209,7 @@
         <v>86</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -3981,7 +3980,7 @@
       <c r="K79">
         <v>1000</v>
       </c>
-      <c r="L79" s="2" t="s">
+      <c r="L79" t="s">
         <v>199</v>
       </c>
     </row>

--- a/umbrales_color_annexed_19-06-2026.xlsx
+++ b/umbrales_color_annexed_19-06-2026.xlsx
@@ -1,635 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\sdsn\atlas_sdsn_paolo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795D8703-4212-4910-911B-72E82F3B020B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="200">
-  <si>
-    <t>indicator_code</t>
-  </si>
-  <si>
-    <t>ODS</t>
-  </si>
-  <si>
-    <t>Indicador</t>
-  </si>
-  <si>
-    <t>Green_max</t>
-  </si>
-  <si>
-    <t>Green_min</t>
-  </si>
-  <si>
-    <t>Yellow_max</t>
-  </si>
-  <si>
-    <t>Yellow_min</t>
-  </si>
-  <si>
-    <t>Orange_max</t>
-  </si>
-  <si>
-    <t>Orange_min</t>
-  </si>
-  <si>
-    <t>Red_max</t>
-  </si>
-  <si>
-    <t>Red_min</t>
-  </si>
-  <si>
-    <t>Criterio umbral verde</t>
-  </si>
-  <si>
-    <t>01_02_02_01_mpi</t>
-  </si>
-  <si>
-    <t>Índice de Pobreza Multidimensional</t>
-  </si>
-  <si>
-    <t>Meta 1.2  Para 2030, reducir al menos a la mitad la proporción de hombres, mujeres y niños y niñas de todas las edades que viven en la pobreza en todas sus dimensiones con arreglo a las definiciones nacionales.</t>
-  </si>
-  <si>
-    <t>01_04_01_02_eep</t>
-  </si>
-  <si>
-    <t>Tasa de Pobreza Enegética</t>
-  </si>
-  <si>
-    <t>Atlas Municipal de los ODS 2020</t>
-  </si>
-  <si>
-    <t>01_04_01_03_nbi</t>
-  </si>
-  <si>
-    <t>Necesidades Básicas Insatisfechas</t>
-  </si>
-  <si>
-    <t>01_04_02_04_ssb</t>
-  </si>
-  <si>
-    <t>Acceso a los 3 servicios básicos, 2024 (% de hogares)</t>
-  </si>
-  <si>
-    <t>02_02_02_01_smu</t>
-  </si>
-  <si>
-    <t>Obesidad en mujeres (15-49 años)</t>
-  </si>
-  <si>
-    <t>SDG Index Global</t>
-  </si>
-  <si>
-    <t>02_02_02_02_dcn</t>
-  </si>
-  <si>
-    <t>Desnutrición crónica niños &lt; 5 años</t>
-  </si>
-  <si>
-    <t>02_02_02_03_osn</t>
-  </si>
-  <si>
-    <t>Obesidad en niños &lt; 5 años</t>
-  </si>
-  <si>
-    <t>Plan sectorial de desarrollo integral para vivir bien - Sector Salud 2021-2025</t>
-  </si>
-  <si>
-    <t>02_02_03_04_pam</t>
-  </si>
-  <si>
-    <t>Prevalencia de anemia en mujeres (15-49 años)</t>
-  </si>
-  <si>
-    <t>Organización Mundial de la Salud (Plan on maternal, infant and young child nutrition)</t>
-  </si>
-  <si>
-    <t>02_03_01_05_pac</t>
-  </si>
-  <si>
-    <t>Producción agrícola per cápita</t>
-  </si>
-  <si>
-    <t>Promedio + desviación estandar</t>
-  </si>
-  <si>
-    <t>02_03_01_06_rpa</t>
-  </si>
-  <si>
-    <t>Rendimiento agrícola (Tm/Ha)</t>
-  </si>
-  <si>
-    <t>02_05_01_07_idp</t>
-  </si>
-  <si>
-    <t>Índice de diversificación productiva con base SIIP</t>
-  </si>
-  <si>
-    <t>03_01_02_01_cpp</t>
-  </si>
-  <si>
-    <t>Cobertura de partos atendidos por personal de salud calificado(%)</t>
-  </si>
-  <si>
-    <t>03_02_01_02_tmi</t>
-  </si>
-  <si>
-    <t>Tasa de mortalidad infantil (&lt; 1 año) (por 1,000 nacidos vivos)</t>
-  </si>
-  <si>
-    <t>03_02_01_03_tmn</t>
-  </si>
-  <si>
-    <t>Tasa de mortalidad en niños (&lt; 5 años) (por 1,000 nacidos vivos)</t>
-  </si>
-  <si>
-    <t>03_03_01_04_vih</t>
-  </si>
-  <si>
-    <t>Incidencia de VIH por 1.000.000 habitantes en el periodo 2011-2013 y 2022-2024</t>
-  </si>
-  <si>
-    <t>10% del promedio nacional del 2012</t>
-  </si>
-  <si>
-    <t>03_03_02_05_tub</t>
-  </si>
-  <si>
-    <t>Incidencia de Tuberculosis por 100.000 habitantes en el periodo 2011-2013 y 2022-2024</t>
-  </si>
-  <si>
-    <t>03_03_03_06_vec</t>
-  </si>
-  <si>
-    <t>Tasa de enfermedades por vectores (Chagas, Malaria, Dengue) en el periodo 2011-2013 y 2022-2024</t>
-  </si>
-  <si>
-    <t>Metas de los programas nacionales e internacionales</t>
-  </si>
-  <si>
-    <t>03_07_02_07_tfa</t>
-  </si>
-  <si>
-    <t>Paridez media en adolescentes (15 a 19 años)</t>
-  </si>
-  <si>
-    <t>Desviacion estandar de valores del 2012</t>
-  </si>
-  <si>
-    <t>04_01_02_01_asm</t>
-  </si>
-  <si>
-    <t>Tasa de abandono escolar de mujeres en secundaria (Abandono/Matriculación) (%)</t>
-  </si>
-  <si>
-    <t>04_01_02_02_ash</t>
-  </si>
-  <si>
-    <t>Tasa de abandono escolar de hombres en secundaria (Abandono/Matriculación) (%)</t>
-  </si>
-  <si>
-    <t>04_02_02_03_tam</t>
-  </si>
-  <si>
-    <t>Tasa de asistencia a un establecimiento educativo de niñas de 4 a 5 años de edad</t>
-  </si>
-  <si>
-    <t>04_02_02_04_tah</t>
-  </si>
-  <si>
-    <t>Tasa de asistencia a un establecimiento educativo de niños de 4 a 5 años de edad</t>
-  </si>
-  <si>
-    <t>04_03_02_05_aem</t>
-  </si>
-  <si>
-    <t>Promedio de años de educación mujeres (edad 25 a 35)</t>
-  </si>
-  <si>
-    <t>Criterio de expertos con base en el Panorama Social de América Latina 2019 de CEPAL (Comisión Económica para América Latina y el Caribe)</t>
-  </si>
-  <si>
-    <t>04_03_02_06_aeh</t>
-  </si>
-  <si>
-    <t>Promedio de años de educación hombres (edad 25 a 35)</t>
-  </si>
-  <si>
-    <t>04_03_04_07_esm</t>
-  </si>
-  <si>
-    <t>Porcentaje de población de 19 años o mas con nivel de educación superior alcanzado (mujeres)</t>
-  </si>
-  <si>
-    <t>04_03_04_08_esh</t>
-  </si>
-  <si>
-    <t>Porcentaje de población de 19 años o mas con nivel de educación superior alcanzado (hombres)</t>
-  </si>
-  <si>
-    <t>04_06_01_09_alf</t>
-  </si>
-  <si>
-    <t>Tasa de alfabetización de personas de 15 años o más (%)</t>
-  </si>
-  <si>
-    <t>04_10_01_10_pci</t>
-  </si>
-  <si>
-    <t>Profesores calificados en nivel inicial</t>
-  </si>
-  <si>
-    <t>04_10_01_11_pcs</t>
-  </si>
-  <si>
-    <t>Profesores calificados en nivel secundario</t>
-  </si>
-  <si>
-    <t>05_01_01_01_pga</t>
-  </si>
-  <si>
-    <t>Paridad de género en abandono escolar en secundaria</t>
-  </si>
-  <si>
-    <t>05_01_01_02_pgm</t>
-  </si>
-  <si>
-    <t>Paridad de género en el índice de pobreza multidimensional</t>
-  </si>
-  <si>
-    <t>Alcanzar la paridad de género en el índice de pobreza multidimensional = 1</t>
-  </si>
-  <si>
-    <t>05_01_01_03_pge</t>
-  </si>
-  <si>
-    <t>Índice de paridad de género para años de estudio de la población de 25 a 35 años (mujeres/hombres)</t>
-  </si>
-  <si>
-    <t>05_01_01_04_pgp</t>
-  </si>
-  <si>
-    <t>Paridad de género en la tasa global de participación (≥14 años)</t>
-  </si>
-  <si>
-    <t>Paridad alcanzada</t>
-  </si>
-  <si>
-    <t>05_04_01_05_phc</t>
-  </si>
-  <si>
-    <t>Paridad de género en labores del hogar o labores de cuidado (15-24 años)</t>
-  </si>
-  <si>
-    <t>05_05_01_06_acm</t>
-  </si>
-  <si>
-    <t>Porcentaje de concejales mujeres</t>
-  </si>
-  <si>
-    <t>06_01_01_01_cap</t>
-  </si>
-  <si>
-    <t>Cobertura de agua potable</t>
-  </si>
-  <si>
-    <t>06_02_01_02_cas</t>
-  </si>
-  <si>
-    <t>Cobertura de saneamiento</t>
-  </si>
-  <si>
-    <t>06_03_01_03_tar</t>
-  </si>
-  <si>
-    <t>Índice de tratamiento de agua residual</t>
-  </si>
-  <si>
-    <t>07_01_01_01_cep</t>
-  </si>
-  <si>
-    <t>Consumo de electricidad residencial per cápita</t>
-  </si>
-  <si>
-    <t>World Bank, 2025. An Evaluation of the World Bank Group's Support to Electricity Access in Sub-Saharan Africa, 2015-24</t>
-  </si>
-  <si>
-    <t>07_01_01_02_cae</t>
-  </si>
-  <si>
-    <t>Cobertura de energía eléctrica, (% de población)</t>
-  </si>
-  <si>
-    <t>07_01_01_03_mcc</t>
-  </si>
-  <si>
-    <t>Porcentaje de medidores eléctricos residenciales con consumo cero</t>
-  </si>
-  <si>
-    <t>07_01_02_04_elc</t>
-  </si>
-  <si>
-    <t>Energía limpia para cocinar</t>
-  </si>
-  <si>
-    <t>08_05_02_01_tgm</t>
-  </si>
-  <si>
-    <t>Tasa global de participación mujeres (≥ 14 años), (%)</t>
-  </si>
-  <si>
-    <t>Prom + desviación estandar</t>
-  </si>
-  <si>
-    <t>08_05_02_02_tgh</t>
-  </si>
-  <si>
-    <t>Tasa global de participación hombres (≥ 14 años), (%)</t>
-  </si>
-  <si>
-    <t>08_06_01_03_etm</t>
-  </si>
-  <si>
-    <t>Proporción de mujeres que no estudian, ni participan en el mercado laboral (15-24 años)(%)</t>
-  </si>
-  <si>
-    <t>08_06_01_04_eth</t>
-  </si>
-  <si>
-    <t>Propoción de hombres que no estudian, ni participan en el mercado laboral (15-24 años)</t>
-  </si>
-  <si>
-    <t>08_09_02_05_pot</t>
-  </si>
-  <si>
-    <t>Porcentaje de población ocupada de 14 o más años de edad en actividades económicas relacionadas con el turismo</t>
-  </si>
-  <si>
-    <t>Criterio nacional / meta sectorial de referencia del PSDI Turismo 2021–2025</t>
-  </si>
-  <si>
-    <t>08_09_02_06_pbt</t>
-  </si>
-  <si>
-    <t>Porcentaje del PIB que corresponde a turismo</t>
-  </si>
-  <si>
-    <t>08_10_02_07_dsb</t>
-  </si>
-  <si>
-    <t>Densidad de sucursales bancarias  por 100.000 habitantes</t>
-  </si>
-  <si>
-    <t>09_01_01_01_vpc</t>
-  </si>
-  <si>
-    <t>Cantidad de vias fundamentales que pasan dentro de un municipio</t>
-  </si>
-  <si>
-    <t>Promedio de los valores del 2012</t>
-  </si>
-  <si>
-    <t>09_08_01_02_ci</t>
-  </si>
-  <si>
-    <t>Porcentaje de hogares con acceso a internet (%)</t>
-  </si>
-  <si>
-    <t>Criterio de expertos con base en UIT(Unión Internacional de Telecomunicaciones)</t>
-  </si>
-  <si>
-    <t>09_08_01_03_drb</t>
-  </si>
-  <si>
-    <t>Densidad de radiobases</t>
-  </si>
-  <si>
-    <t>Maximo - promedio + Desv Estandar de valores del 2012</t>
-  </si>
-  <si>
-    <t>09_08_01_04_tfc</t>
-  </si>
-  <si>
-    <t>Porcentaje de hogares con cobertura de telefonía fija o celular</t>
-  </si>
-  <si>
-    <t>10_02_01_01_esp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de la población de 3 años o mas, que no hablan español (como su lengua materna, primero o segundo idioma)
-</t>
-  </si>
-  <si>
-    <t>10_02_01_02_pel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brecha de pobreza multidimensional según autoidentificación indígena
-</t>
-  </si>
-  <si>
-    <t>Alcanzar la paridad entre sub poblaciones con el índice de pobreza multidimensional = 1</t>
-  </si>
-  <si>
-    <t>10_02_01_03_mre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brecha de pobreza migrantes/no-migrantes
-</t>
-  </si>
-  <si>
-    <t>10_02_01_04_tpm</t>
-  </si>
-  <si>
-    <t>Brecha de pobreza multidimensional entre hogares con jefe adulto mayor y sin jefe adulto mayor</t>
-  </si>
-  <si>
-    <t>10_02_01_05_gip</t>
-  </si>
-  <si>
-    <t>Gini del Índice de Pobreza Multidimensional</t>
-  </si>
-  <si>
-    <t>10_04_02_06_gin</t>
-  </si>
-  <si>
-    <t>Coeﬁciente de Gini de años de educación</t>
-  </si>
-  <si>
-    <t>11_01_01_01_thm</t>
-  </si>
-  <si>
-    <t>Tasa de hacinamiento</t>
-  </si>
-  <si>
-    <t>11_01_01_02_ssb</t>
-  </si>
-  <si>
-    <t>Hogares que no tienen servicio sanitario, baño o letrina (%)</t>
-  </si>
-  <si>
-    <t>11_01_01_03_ava</t>
-  </si>
-  <si>
-    <t>Porcentaje de viviendas adecuadas</t>
-  </si>
-  <si>
-    <t>Prom + 3*desviación estandar</t>
-  </si>
-  <si>
-    <t>11_02_01_04_atc</t>
-  </si>
-  <si>
-    <t>Asientos disponibles en el transporte colectivo por cada mil habitantes</t>
-  </si>
-  <si>
-    <t>11_06_01_05_ipr</t>
-  </si>
-  <si>
-    <t>Inversión pública municipal en residuos sólidos per cápita</t>
-  </si>
-  <si>
-    <t>BID, 2023. Sostenibilidad financiera de la gestión de residuos sólidos en América Latina y el Caribe</t>
-  </si>
-  <si>
-    <t>11_06_01_06_srr</t>
-  </si>
-  <si>
-    <t>Porcentaje de población con recolección de residuos</t>
-  </si>
-  <si>
-    <t>Criterio de expertos</t>
-  </si>
-  <si>
-    <t>11_06_02_07_ica</t>
-  </si>
-  <si>
-    <t>Concentracion promedio de PM 2.5 en manzanos , 2010-2012 y 2021-2023</t>
-  </si>
-  <si>
-    <t>Criterios y metas de la OMS</t>
-  </si>
-  <si>
-    <t>13_01_01_01_fec</t>
-  </si>
-  <si>
-    <t>Porcentaje de familias afectadas por eventos climáticos</t>
-  </si>
-  <si>
-    <t>13_01_03_02_icc</t>
-  </si>
-  <si>
-    <t>Indice de Vulnerabilidad al Cambio Climatico</t>
-  </si>
-  <si>
-    <t>13_02_02_03_epb</t>
-  </si>
-  <si>
-    <t>Emisiones de CO2 por pérdida de bosque per cápita</t>
-  </si>
-  <si>
-    <t>13_02_02_04_ect</t>
-  </si>
-  <si>
-    <t>Emisiones de CO2 por transporte per cápita</t>
-  </si>
-  <si>
-    <t>Promedio +/- desviación estandar</t>
-  </si>
-  <si>
-    <t>13_02_02_05_eci</t>
-  </si>
-  <si>
-    <t>Emisiones totales de CO2 por degradación por incendios per cápita</t>
-  </si>
-  <si>
-    <t>15_01_02_01_sap</t>
-  </si>
-  <si>
-    <t>Porcentaje de superficie de áreas protegidas por municipio</t>
-  </si>
-  <si>
-    <t>15_02_01_02_tpb</t>
-  </si>
-  <si>
-    <t>Tasa promedio de pérdida de bosque</t>
-  </si>
-  <si>
-    <t>15_05_02_03_pbd</t>
-  </si>
-  <si>
-    <t>Índice de pérdida de biodiversidad por deforestación</t>
-  </si>
-  <si>
-    <t>15_05_02_04_pbi</t>
-  </si>
-  <si>
-    <t>16_01_01_01_thp</t>
-  </si>
-  <si>
-    <t>Tasa de Homicidios por 100.000 habitantes en el periodo 2017-2019 y 2022-2024</t>
-  </si>
-  <si>
-    <t>16_06_01_02_cep</t>
-  </si>
-  <si>
-    <t>Porcentaje de presupuesto total que ha sido ejecutado</t>
-  </si>
-  <si>
-    <t>Atlas Municipal de los ODS / Barja, 2025. Viabilidad Municipal en Bolivia</t>
-  </si>
-  <si>
-    <t>16_07_02_03_tcs</t>
-  </si>
-  <si>
-    <t>Cantidad de conflictos</t>
-  </si>
-  <si>
-    <t>16_09_01_04_nic</t>
-  </si>
-  <si>
-    <t>Niños inscritos en el registro civil (&lt; 5 años)</t>
-  </si>
-  <si>
-    <t>17_01_02_01_iil</t>
-  </si>
-  <si>
-    <t>Porcentaje de ingresos que proviene de fuentes locales</t>
-  </si>
-  <si>
-    <t>17_18_01_02_ipc</t>
-  </si>
-  <si>
-    <t>Inversión pública per cápita</t>
-  </si>
-  <si>
-    <t>Criterio de expertos (Taller externo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta 16.1 Reducir significativamente todas las formas de violencia y las correspondientes tasas de mortalidad en todo el mundo </t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -729,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -763,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -798,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -974,70 +350,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="30.21875" customWidth="1"/>
-    <col min="12" max="12" width="7.77734375" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>indicator_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Green_max</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Green_min</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Yellow_max</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Yellow_min</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Orange_max</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Orange_min</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Red_max</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Red_min</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Criterio umbral verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01_02_02_01_mpi</t>
+        </is>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Índice de Pobreza Multidimensional</t>
+        </is>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G2">
         <v>0.13</v>
@@ -1054,19 +454,25 @@
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>15</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meta 1.2  Para 2030, reducir al menos a la mitad la proporción de hombres, mujeres y niños y niñas de todas las edades que viven en la pobreza en todas sus dimensiones con arreglo a las definiciones nacionales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>01_04_01_02_eep</t>
+        </is>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tasa de Pobreza Enegética</t>
+        </is>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1092,19 +498,25 @@
       <c r="K3">
         <v>100</v>
       </c>
-      <c r="L3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>01_04_01_03_nbi</t>
+        </is>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Necesidades Básicas Insatisfechas</t>
+        </is>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1130,19 +542,25 @@
       <c r="K4">
         <v>100</v>
       </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>20</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>01_04_02_04_ssb</t>
+        </is>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Acceso a los 3 servicios básicos, 2024 (% de hogares)</t>
+        </is>
       </c>
       <c r="D5">
         <v>100</v>
@@ -1168,19 +586,25 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>22</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>02_02_02_01_smu</t>
+        </is>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Obesidad en mujeres (15-49 años)</t>
+        </is>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1206,19 +630,25 @@
       <c r="K6">
         <v>100</v>
       </c>
-      <c r="L6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>25</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>02_02_02_02_dcn</t>
+        </is>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Desnutrición crónica niños &lt; 5 años</t>
+        </is>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1244,19 +674,25 @@
       <c r="K7">
         <v>100</v>
       </c>
-      <c r="L7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>27</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>02_02_02_03_osn</t>
+        </is>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Obesidad en niños &lt; 5 años</t>
+        </is>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1282,19 +718,25 @@
       <c r="K8">
         <v>100</v>
       </c>
-      <c r="L8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>30</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Plan sectorial de desarrollo integral para vivir bien - Sector Salud 2021-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>02_02_03_04_pam</t>
+        </is>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
-        <v>31</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prevalencia de anemia en mujeres (15-49 años)</t>
+        </is>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1320,19 +762,25 @@
       <c r="K9">
         <v>100</v>
       </c>
-      <c r="L9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>33</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Organización Mundial de la Salud (Plan on maternal, infant and young child nutrition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>02_03_01_05_pac</t>
+        </is>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" t="s">
-        <v>34</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Producción agrícola per cápita</t>
+        </is>
       </c>
       <c r="D10">
         <v>999</v>
@@ -1350,27 +798,33 @@
         <v>2</v>
       </c>
       <c r="I10">
-        <v>1.0000000000000001E-5</v>
+        <v>0.1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>36</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Promedio + desviación estandar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>02_03_01_06_rpa</t>
+        </is>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
-        <v>37</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rendimiento agrícola (Tm/Ha)</t>
+        </is>
       </c>
       <c r="D11">
         <v>999</v>
@@ -1396,19 +850,25 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>38</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>02_05_01_07_idp</t>
+        </is>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" t="s">
-        <v>39</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Índice de diversificación productiva con base SIIP</t>
+        </is>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1434,19 +894,25 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>40</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Promedio + desviación estandar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>03_01_02_01_cpp</t>
+        </is>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
-        <v>41</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cobertura de partos atendidos por personal de salud calificado(%)</t>
+        </is>
       </c>
       <c r="D13">
         <v>100</v>
@@ -1472,19 +938,25 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>42</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>03_02_01_02_tmi</t>
+        </is>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14" t="s">
-        <v>43</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil (&lt; 1 año) (por 1,000 nacidos vivos)</t>
+        </is>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1510,19 +982,25 @@
       <c r="K14">
         <v>400</v>
       </c>
-      <c r="L14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>44</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>03_02_01_03_tmn</t>
+        </is>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
-      <c r="C15" t="s">
-        <v>45</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad en niños (&lt; 5 años) (por 1,000 nacidos vivos)</t>
+        </is>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1548,19 +1026,25 @@
       <c r="K15">
         <v>300</v>
       </c>
-      <c r="L15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>46</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>03_03_01_04_vih</t>
+        </is>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16" t="s">
-        <v>47</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Incidencia de VIH por 1.000.000 habitantes en el periodo 2011-2013 y 2022-2024</t>
+        </is>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1586,19 +1070,25 @@
       <c r="K16">
         <v>20000</v>
       </c>
-      <c r="L16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>49</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10% del promedio nacional del 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>03_03_02_05_tub</t>
+        </is>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
-      <c r="C17" t="s">
-        <v>50</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Incidencia de Tuberculosis por 100.000 habitantes en el periodo 2011-2013 y 2022-2024</t>
+        </is>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1624,19 +1114,25 @@
       <c r="K17">
         <v>433.4</v>
       </c>
-      <c r="L17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>51</v>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>03_03_03_06_vec</t>
+        </is>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
-      <c r="C18" t="s">
-        <v>52</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tasa de enfermedades por vectores (Chagas, Malaria, Dengue) en el periodo 2011-2013 y 2022-2024</t>
+        </is>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1645,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>9.9999999999999995E-7</v>
+        <v>1E-07</v>
       </c>
       <c r="G18">
         <v>0.1</v>
@@ -1662,19 +1158,25 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="L18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>54</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Metas de los programas nacionales e internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>03_07_02_07_tfa</t>
+        </is>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19" t="s">
-        <v>55</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Paridez media en adolescentes (15 a 19 años)</t>
+        </is>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1700,19 +1202,25 @@
       <c r="K19">
         <v>1.17</v>
       </c>
-      <c r="L19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>57</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Desviacion estandar de valores del 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>04_01_02_01_asm</t>
+        </is>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20" t="s">
-        <v>58</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tasa de abandono escolar de mujeres en secundaria (Abandono/Matriculación) (%)</t>
+        </is>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1738,19 +1246,25 @@
       <c r="K20">
         <v>100</v>
       </c>
-      <c r="L20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>59</v>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>04_01_02_02_ash</t>
+        </is>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
-      <c r="C21" t="s">
-        <v>60</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tasa de abandono escolar de hombres en secundaria (Abandono/Matriculación) (%)</t>
+        </is>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1776,19 +1290,25 @@
       <c r="K21">
         <v>100</v>
       </c>
-      <c r="L21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>61</v>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>04_02_02_03_tam</t>
+        </is>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22" t="s">
-        <v>62</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tasa de asistencia a un establecimiento educativo de niñas de 4 a 5 años de edad</t>
+        </is>
       </c>
       <c r="D22">
         <v>100</v>
@@ -1814,19 +1334,25 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>63</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>04_02_02_04_tah</t>
+        </is>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23" t="s">
-        <v>64</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tasa de asistencia a un establecimiento educativo de niños de 4 a 5 años de edad</t>
+        </is>
       </c>
       <c r="D23">
         <v>100</v>
@@ -1852,19 +1378,25 @@
       <c r="K23">
         <v>18</v>
       </c>
-      <c r="L23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>65</v>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>04_03_02_05_aem</t>
+        </is>
       </c>
       <c r="B24">
         <v>4</v>
       </c>
-      <c r="C24" t="s">
-        <v>66</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Promedio de años de educación mujeres (edad 25 a 35)</t>
+        </is>
       </c>
       <c r="D24">
         <v>20</v>
@@ -1890,19 +1422,25 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>68</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Criterio de expertos con base en el Panorama Social de América Latina 2019 de CEPAL (Comisión Económica para América Latina y el Caribe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>04_03_02_06_aeh</t>
+        </is>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25" t="s">
-        <v>69</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Promedio de años de educación hombres (edad 25 a 35)</t>
+        </is>
       </c>
       <c r="D25">
         <v>20</v>
@@ -1928,19 +1466,25 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="L25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>70</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Criterio de expertos con base en el Panorama Social de América Latina 2019 de CEPAL (Comisión Económica para América Latina y el Caribe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>04_03_04_07_esm</t>
+        </is>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26" t="s">
-        <v>71</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Porcentaje de población de 19 años o mas con nivel de educación superior alcanzado (mujeres)</t>
+        </is>
       </c>
       <c r="D26">
         <v>100</v>
@@ -1966,19 +1510,25 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>72</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>04_03_04_08_esh</t>
+        </is>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
-      <c r="C27" t="s">
-        <v>73</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Porcentaje de población de 19 años o mas con nivel de educación superior alcanzado (hombres)</t>
+        </is>
       </c>
       <c r="D27">
         <v>100</v>
@@ -2004,19 +1554,25 @@
       <c r="K27">
         <v>0</v>
       </c>
-      <c r="L27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>74</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>04_06_01_09_alf</t>
+        </is>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
-      <c r="C28" t="s">
-        <v>75</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tasa de alfabetización de personas de 15 años o más (%)</t>
+        </is>
       </c>
       <c r="D28">
         <v>100</v>
@@ -2042,34 +1598,40 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>76</v>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>04_10_01_10_pci</t>
+        </is>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29" t="s">
-        <v>77</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Profesores calificados en nivel inicial</t>
+        </is>
       </c>
       <c r="D29">
         <v>100</v>
       </c>
       <c r="E29">
-        <v>96.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F29">
-        <v>96.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G29">
-        <v>69.599999999999994</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H29">
-        <v>69.599999999999994</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I29">
         <v>42.3</v>
@@ -2080,34 +1642,40 @@
       <c r="K29">
         <v>0</v>
       </c>
-      <c r="L29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>78</v>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>04_10_01_11_pcs</t>
+        </is>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30" t="s">
-        <v>79</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Profesores calificados en nivel secundario</t>
+        </is>
       </c>
       <c r="D30">
         <v>100</v>
       </c>
       <c r="E30">
-        <v>96.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F30">
-        <v>96.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G30">
-        <v>69.599999999999994</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H30">
-        <v>69.599999999999994</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I30">
         <v>42.3</v>
@@ -2118,19 +1686,25 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>80</v>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>05_01_01_01_pga</t>
+        </is>
       </c>
       <c r="B31">
         <v>5</v>
       </c>
-      <c r="C31" t="s">
-        <v>81</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Paridad de género en abandono escolar en secundaria</t>
+        </is>
       </c>
       <c r="D31">
         <v>8</v>
@@ -2156,19 +1730,25 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>82</v>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Paridad alcanzada</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>05_01_01_02_pgm</t>
+        </is>
       </c>
       <c r="B32">
         <v>5</v>
       </c>
-      <c r="C32" t="s">
-        <v>83</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Paridad de género en el índice de pobreza multidimensional</t>
+        </is>
       </c>
       <c r="D32">
         <v>999</v>
@@ -2194,22 +1774,28 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>85</v>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Paridad alcanzada</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>05_01_01_03_pge</t>
+        </is>
       </c>
       <c r="B33">
         <v>5</v>
       </c>
-      <c r="C33" t="s">
-        <v>86</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Índice de paridad de género para años de estudio de la población de 25 a 35 años (mujeres/hombres)</t>
+        </is>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2232,19 +1818,26 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>87</v>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paridad alcanzada_x000D_
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>05_01_01_04_pgp</t>
+        </is>
       </c>
       <c r="B34">
         <v>5</v>
       </c>
-      <c r="C34" t="s">
-        <v>88</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Paridad de género en la tasa global de participación (≥14 años)</t>
+        </is>
       </c>
       <c r="D34">
         <v>3</v>
@@ -2270,19 +1863,25 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="L34" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>90</v>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Paridad alcanzada</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>05_04_01_05_phc</t>
+        </is>
       </c>
       <c r="B35">
         <v>5</v>
       </c>
-      <c r="C35" t="s">
-        <v>91</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Paridad de género en labores del hogar o labores de cuidado (15-24 años)</t>
+        </is>
       </c>
       <c r="D35">
         <v>3</v>
@@ -2308,19 +1907,25 @@
       <c r="K35">
         <v>0</v>
       </c>
-      <c r="L35" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>92</v>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Paridad alcanzada</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>05_05_01_06_acm</t>
+        </is>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
-      <c r="C36" t="s">
-        <v>93</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Porcentaje de concejales mujeres</t>
+        </is>
       </c>
       <c r="D36">
         <v>100</v>
@@ -2346,19 +1951,25 @@
       <c r="K36">
         <v>0</v>
       </c>
-      <c r="L36" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>94</v>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>06_01_01_01_cap</t>
+        </is>
       </c>
       <c r="B37">
         <v>6</v>
       </c>
-      <c r="C37" t="s">
-        <v>95</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cobertura de agua potable</t>
+        </is>
       </c>
       <c r="D37">
         <v>100</v>
@@ -2384,19 +1995,25 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>96</v>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>06_02_01_02_cas</t>
+        </is>
       </c>
       <c r="B38">
         <v>6</v>
       </c>
-      <c r="C38" t="s">
-        <v>97</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cobertura de saneamiento</t>
+        </is>
       </c>
       <c r="D38">
         <v>100</v>
@@ -2422,19 +2039,25 @@
       <c r="K38">
         <v>0</v>
       </c>
-      <c r="L38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>98</v>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>06_03_01_03_tar</t>
+        </is>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
-      <c r="C39" t="s">
-        <v>99</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Índice de tratamiento de agua residual</t>
+        </is>
       </c>
       <c r="D39">
         <v>500</v>
@@ -2460,19 +2083,25 @@
       <c r="K39">
         <v>0</v>
       </c>
-      <c r="L39" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>100</v>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>07_01_01_01_cep</t>
+        </is>
       </c>
       <c r="B40">
         <v>7</v>
       </c>
-      <c r="C40" t="s">
-        <v>101</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Consumo de electricidad residencial per cápita</t>
+        </is>
       </c>
       <c r="D40">
         <v>1700</v>
@@ -2498,19 +2127,25 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>103</v>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>World Bank, 2025. An Evaluation of the World Bank Group's Support to Electricity Access in Sub-Saharan Africa, 2015-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>07_01_01_02_cae</t>
+        </is>
       </c>
       <c r="B41">
         <v>7</v>
       </c>
-      <c r="C41" t="s">
-        <v>104</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Cobertura de energía eléctrica, (% de población)</t>
+        </is>
       </c>
       <c r="D41">
         <v>100</v>
@@ -2536,19 +2171,25 @@
       <c r="K41">
         <v>0</v>
       </c>
-      <c r="L41" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>105</v>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>07_01_01_03_mcc</t>
+        </is>
       </c>
       <c r="B42">
         <v>7</v>
       </c>
-      <c r="C42" t="s">
-        <v>106</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Porcentaje de medidores eléctricos residenciales con consumo cero</t>
+        </is>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2560,10 +2201,10 @@
         <v>4.5</v>
       </c>
       <c r="G42">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H42">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="I42">
         <v>24.9</v>
@@ -2574,19 +2215,25 @@
       <c r="K42">
         <v>100</v>
       </c>
-      <c r="L42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>107</v>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>07_01_02_04_elc</t>
+        </is>
       </c>
       <c r="B43">
         <v>7</v>
       </c>
-      <c r="C43" t="s">
-        <v>108</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Energía limpia para cocinar</t>
+        </is>
       </c>
       <c r="D43">
         <v>100</v>
@@ -2612,19 +2259,25 @@
       <c r="K43">
         <v>0</v>
       </c>
-      <c r="L43" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>109</v>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>08_05_02_01_tgm</t>
+        </is>
       </c>
       <c r="B44">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
-        <v>110</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tasa global de participación mujeres (≥ 14 años), (%)</t>
+        </is>
       </c>
       <c r="D44">
         <v>100</v>
@@ -2650,19 +2303,25 @@
       <c r="K44">
         <v>0</v>
       </c>
-      <c r="L44" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>112</v>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Prom + desviación estandar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>08_05_02_02_tgh</t>
+        </is>
       </c>
       <c r="B45">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
-        <v>113</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tasa global de participación hombres (≥ 14 años), (%)</t>
+        </is>
       </c>
       <c r="D45">
         <v>100</v>
@@ -2688,19 +2347,25 @@
       <c r="K45">
         <v>0</v>
       </c>
-      <c r="L45" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>114</v>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Prom + desviación estandar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>08_06_01_03_etm</t>
+        </is>
       </c>
       <c r="B46">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
-        <v>115</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Proporción de mujeres que no estudian, ni participan en el mercado laboral (15-24 años)(%)</t>
+        </is>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2726,19 +2391,25 @@
       <c r="K46">
         <v>100</v>
       </c>
-      <c r="L46" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>116</v>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>08_06_01_04_eth</t>
+        </is>
       </c>
       <c r="B47">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
-        <v>117</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Propoción de hombres que no estudian, ni participan en el mercado laboral (15-24 años)</t>
+        </is>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2764,19 +2435,25 @@
       <c r="K47">
         <v>100</v>
       </c>
-      <c r="L47" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>118</v>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>08_09_02_05_pot</t>
+        </is>
       </c>
       <c r="B48">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
-        <v>119</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Porcentaje de población ocupada de 14 o más años de edad en actividades económicas relacionadas con el turismo</t>
+        </is>
       </c>
       <c r="D48">
         <v>13</v>
@@ -2802,19 +2479,25 @@
       <c r="K48">
         <v>0</v>
       </c>
-      <c r="L48" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>121</v>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Criterio nacional / meta sectorial de referencia del PSDI Turismo 2021–2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>08_09_02_06_pbt</t>
+        </is>
       </c>
       <c r="B49">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
-        <v>122</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Porcentaje del PIB que corresponde a turismo</t>
+        </is>
       </c>
       <c r="D49">
         <v>100</v>
@@ -2840,19 +2523,25 @@
       <c r="K49">
         <v>0</v>
       </c>
-      <c r="L49" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>123</v>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Criterio nacional / meta sectorial de referencia del PSDI Turismo 2021–2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>08_10_02_07_dsb</t>
+        </is>
       </c>
       <c r="B50">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
-        <v>124</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Densidad de sucursales bancarias  por 100.000 habitantes</t>
+        </is>
       </c>
       <c r="D50">
         <v>225</v>
@@ -2878,22 +2567,28 @@
       <c r="K50">
         <v>0</v>
       </c>
-      <c r="L50" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>125</v>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>09_01_01_01_vpc</t>
+        </is>
       </c>
       <c r="B51">
         <v>9</v>
       </c>
-      <c r="C51" t="s">
-        <v>126</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cantidad de vias fundamentales que pasan dentro de un municipio</t>
+        </is>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51">
         <v>2</v>
@@ -2908,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1E-05</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -2916,19 +2611,25 @@
       <c r="K51">
         <v>0</v>
       </c>
-      <c r="L51" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>128</v>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Promedio de los valores del 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>09_08_01_02_ci</t>
+        </is>
       </c>
       <c r="B52">
         <v>9</v>
       </c>
-      <c r="C52" t="s">
-        <v>129</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Porcentaje de hogares con acceso a internet (%)</t>
+        </is>
       </c>
       <c r="D52">
         <v>100</v>
@@ -2954,19 +2655,25 @@
       <c r="K52">
         <v>0</v>
       </c>
-      <c r="L52" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>131</v>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Criterio de expertos con base en UIT(Unión Internacional de Telecomunicaciones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>09_08_01_03_drb</t>
+        </is>
       </c>
       <c r="B53">
         <v>9</v>
       </c>
-      <c r="C53" t="s">
-        <v>132</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Densidad de radiobases</t>
+        </is>
       </c>
       <c r="D53">
         <v>6</v>
@@ -2992,19 +2699,25 @@
       <c r="K53">
         <v>0</v>
       </c>
-      <c r="L53" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>134</v>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Maximo - promedio + Desv Estandar de valores del 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>09_08_01_04_tfc</t>
+        </is>
       </c>
       <c r="B54">
         <v>9</v>
       </c>
-      <c r="C54" t="s">
-        <v>135</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Porcentaje de hogares con cobertura de telefonía fija o celular</t>
+        </is>
       </c>
       <c r="D54">
         <v>100</v>
@@ -3030,19 +2743,26 @@
       <c r="K54">
         <v>0</v>
       </c>
-      <c r="L54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>136</v>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10_02_01_01_esp</t>
+        </is>
       </c>
       <c r="B55">
         <v>10</v>
       </c>
-      <c r="C55" t="s">
-        <v>137</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porcentaje de la población de 3 años o mas, que no hablan español (como su lengua materna, primero o segundo idioma)
+</t>
+        </is>
       </c>
       <c r="D55">
         <v>0</v>
@@ -3068,19 +2788,26 @@
       <c r="K55">
         <v>100</v>
       </c>
-      <c r="L55" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>138</v>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10_02_01_02_pel</t>
+        </is>
       </c>
       <c r="B56">
         <v>10</v>
       </c>
-      <c r="C56" t="s">
-        <v>139</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brecha de pobreza multidimensional según autoidentificación indígena
+</t>
+        </is>
       </c>
       <c r="D56">
         <v>999</v>
@@ -3106,19 +2833,26 @@
       <c r="K56">
         <v>0</v>
       </c>
-      <c r="L56" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>141</v>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Paridad alcanzada</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10_02_01_03_mre</t>
+        </is>
       </c>
       <c r="B57">
         <v>10</v>
       </c>
-      <c r="C57" t="s">
-        <v>142</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brecha de pobreza migrantes/no-migrantes
+</t>
+        </is>
       </c>
       <c r="D57">
         <v>999</v>
@@ -3144,19 +2878,25 @@
       <c r="K57">
         <v>0</v>
       </c>
-      <c r="L57" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>143</v>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Paridad alcanzada</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10_02_01_04_tpm</t>
+        </is>
       </c>
       <c r="B58">
         <v>10</v>
       </c>
-      <c r="C58" t="s">
-        <v>144</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Brecha de pobreza multidimensional entre hogares con jefe adulto mayor y sin jefe adulto mayor</t>
+        </is>
       </c>
       <c r="D58">
         <v>999</v>
@@ -3182,57 +2922,69 @@
       <c r="K58">
         <v>0</v>
       </c>
-      <c r="L58" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>145</v>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Paridad alcanzada</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10_02_01_05_gip</t>
+        </is>
       </c>
       <c r="B59">
         <v>10</v>
       </c>
-      <c r="C59" t="s">
-        <v>146</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Gini del Índice de Pobreza Multidimensional</t>
+        </is>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="F59">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="G59">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="H59">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="I59">
-        <v>0.47</v>
+        <v>0.15</v>
       </c>
       <c r="J59">
-        <v>0.47</v>
+        <v>0.15</v>
       </c>
       <c r="K59">
         <v>1</v>
       </c>
-      <c r="L59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>147</v>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10_04_02_06_gin</t>
+        </is>
       </c>
       <c r="B60">
         <v>10</v>
       </c>
-      <c r="C60" t="s">
-        <v>148</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Coeﬁciente de Gini de años de educación</t>
+        </is>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3258,19 +3010,25 @@
       <c r="K60">
         <v>1</v>
       </c>
-      <c r="L60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>149</v>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>11_01_01_01_thm</t>
+        </is>
       </c>
       <c r="B61">
         <v>11</v>
       </c>
-      <c r="C61" t="s">
-        <v>150</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tasa de hacinamiento</t>
+        </is>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3296,19 +3054,25 @@
       <c r="K61">
         <v>100</v>
       </c>
-      <c r="L61" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>151</v>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>11_01_01_02_ssb</t>
+        </is>
       </c>
       <c r="B62">
         <v>11</v>
       </c>
-      <c r="C62" t="s">
-        <v>152</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hogares que no tienen servicio sanitario, baño o letrina (%)</t>
+        </is>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3334,19 +3098,25 @@
       <c r="K62">
         <v>100</v>
       </c>
-      <c r="L62" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>153</v>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>11_01_01_03_ava</t>
+        </is>
       </c>
       <c r="B63">
         <v>11</v>
       </c>
-      <c r="C63" t="s">
-        <v>154</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Porcentaje de viviendas adecuadas</t>
+        </is>
       </c>
       <c r="D63">
         <v>100</v>
@@ -3372,19 +3142,25 @@
       <c r="K63">
         <v>0</v>
       </c>
-      <c r="L63" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>156</v>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Prom + 3*desviación estandar</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>11_02_01_04_atc</t>
+        </is>
       </c>
       <c r="B64">
         <v>11</v>
       </c>
-      <c r="C64" t="s">
-        <v>157</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Asientos disponibles en el transporte colectivo por cada mil habitantes</t>
+        </is>
       </c>
       <c r="D64">
         <v>5400</v>
@@ -3410,19 +3186,25 @@
       <c r="K64">
         <v>0</v>
       </c>
-      <c r="L64" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>158</v>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>11_06_01_05_ipr</t>
+        </is>
       </c>
       <c r="B65">
         <v>11</v>
       </c>
-      <c r="C65" t="s">
-        <v>159</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Inversión pública municipal en residuos sólidos per cápita</t>
+        </is>
       </c>
       <c r="D65">
         <v>999</v>
@@ -3448,19 +3230,25 @@
       <c r="K65">
         <v>0</v>
       </c>
-      <c r="L65" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>161</v>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>BID, 2023. Sostenibilidad financiera de la gestión de residuos sólidos en América Latina y el Caribe</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>11_06_01_06_srr</t>
+        </is>
       </c>
       <c r="B66">
         <v>11</v>
       </c>
-      <c r="C66" t="s">
-        <v>162</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Porcentaje de población con recolección de residuos</t>
+        </is>
       </c>
       <c r="D66">
         <v>100</v>
@@ -3486,19 +3274,25 @@
       <c r="K66">
         <v>0</v>
       </c>
-      <c r="L66" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>164</v>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Criterio de expertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>11_06_02_07_ica</t>
+        </is>
       </c>
       <c r="B67">
         <v>11</v>
       </c>
-      <c r="C67" t="s">
-        <v>165</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Concentracion promedio de PM 2.5 en manzanos , 2010-2012 y 2021-2023</t>
+        </is>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3524,19 +3318,25 @@
       <c r="K67">
         <v>32</v>
       </c>
-      <c r="L67" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>167</v>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Criterios y metas de la OMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>13_01_01_01_fec</t>
+        </is>
       </c>
       <c r="B68">
         <v>13</v>
       </c>
-      <c r="C68" t="s">
-        <v>168</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Porcentaje de familias afectadas por eventos climáticos</t>
+        </is>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3562,28 +3362,34 @@
       <c r="K68">
         <v>500</v>
       </c>
-      <c r="L68" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>169</v>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Criterio de expertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>13_01_03_02_icc</t>
+        </is>
       </c>
       <c r="B69">
         <v>13</v>
       </c>
-      <c r="C69" t="s">
-        <v>170</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Indice de Vulnerabilidad al Cambio Climatico</t>
+        </is>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F69">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G69">
         <v>1.55</v>
@@ -3600,19 +3406,25 @@
       <c r="K69">
         <v>3</v>
       </c>
-      <c r="L69" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>171</v>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13_02_02_03_epb</t>
+        </is>
       </c>
       <c r="B70">
         <v>13</v>
       </c>
-      <c r="C70" t="s">
-        <v>172</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Emisiones de CO2 por pérdida de bosque per cápita</t>
+        </is>
       </c>
       <c r="D70">
         <v>-20</v>
@@ -3638,19 +3450,25 @@
       <c r="K70">
         <v>450</v>
       </c>
-      <c r="L70" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>173</v>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>13_02_02_04_ect</t>
+        </is>
       </c>
       <c r="B71">
         <v>13</v>
       </c>
-      <c r="C71" t="s">
-        <v>174</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Emisiones de CO2 por transporte per cápita</t>
+        </is>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3659,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-07</v>
       </c>
       <c r="G71">
         <v>0.2</v>
@@ -3676,19 +3494,25 @@
       <c r="K71">
         <v>99</v>
       </c>
-      <c r="L71" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>176</v>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Promedio + desviación estandar</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>13_02_02_05_eci</t>
+        </is>
       </c>
       <c r="B72">
         <v>13</v>
       </c>
-      <c r="C72" t="s">
-        <v>177</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Emisiones totales de CO2 por degradación por incendios per cápita</t>
+        </is>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3714,19 +3538,25 @@
       <c r="K72">
         <v>1300</v>
       </c>
-      <c r="L72" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>178</v>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>15_01_02_01_sap</t>
+        </is>
       </c>
       <c r="B73">
         <v>15</v>
       </c>
-      <c r="C73" t="s">
-        <v>179</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Porcentaje de superficie de áreas protegidas por municipio</t>
+        </is>
       </c>
       <c r="D73">
         <v>100</v>
@@ -3752,19 +3582,25 @@
       <c r="K73">
         <v>0</v>
       </c>
-      <c r="L73" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>180</v>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>15_02_01_02_tpb</t>
+        </is>
       </c>
       <c r="B74">
         <v>15</v>
       </c>
-      <c r="C74" t="s">
-        <v>181</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tasa promedio de pérdida de bosque</t>
+        </is>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3790,19 +3626,25 @@
       <c r="K74">
         <v>100</v>
       </c>
-      <c r="L74" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>182</v>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>15_05_02_03_pbd</t>
+        </is>
       </c>
       <c r="B75">
         <v>15</v>
       </c>
-      <c r="C75" t="s">
-        <v>183</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Índice de pérdida de biodiversidad por deforestación</t>
+        </is>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3828,19 +3670,25 @@
       <c r="K75">
         <v>5</v>
       </c>
-      <c r="L75" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>184</v>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>15_05_02_04_pbi</t>
+        </is>
       </c>
       <c r="B76">
         <v>15</v>
       </c>
-      <c r="C76" t="s">
-        <v>183</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Índice de pérdida de biodiversidad por deforestación</t>
+        </is>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3866,19 +3714,25 @@
       <c r="K76">
         <v>62</v>
       </c>
-      <c r="L76" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>185</v>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16_01_01_01_thp</t>
+        </is>
       </c>
       <c r="B77">
         <v>16</v>
       </c>
-      <c r="C77" t="s">
-        <v>186</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tasa de Homicidios por 100.000 habitantes en el periodo 2017-2019 y 2022-2024</t>
+        </is>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3904,19 +3758,25 @@
       <c r="K77">
         <v>60</v>
       </c>
-      <c r="L77" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>187</v>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16_06_01_02_cep</t>
+        </is>
       </c>
       <c r="B78">
         <v>16</v>
       </c>
-      <c r="C78" t="s">
-        <v>188</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Porcentaje de presupuesto total que ha sido ejecutado</t>
+        </is>
       </c>
       <c r="D78">
         <v>100</v>
@@ -3942,19 +3802,25 @@
       <c r="K78">
         <v>0</v>
       </c>
-      <c r="L78" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>190</v>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS / Barja, 2025. Viabilidad Municipal en Bolivia</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16_07_02_03_tcs</t>
+        </is>
       </c>
       <c r="B79">
         <v>16</v>
       </c>
-      <c r="C79" t="s">
-        <v>191</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cantidad de conflictos</t>
+        </is>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3963,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1E-06</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -3980,19 +3846,25 @@
       <c r="K79">
         <v>1000</v>
       </c>
-      <c r="L79" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>192</v>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Criterio de expertos con base en la Agenda 2030 para el Desarrollo Sostenible de ONU (Organización de las Naciones Unidas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16_09_01_04_nic</t>
+        </is>
       </c>
       <c r="B80">
         <v>16</v>
       </c>
-      <c r="C80" t="s">
-        <v>193</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Niños inscritos en el registro civil (&lt; 5 años)</t>
+        </is>
       </c>
       <c r="D80">
         <v>100</v>
@@ -4018,19 +3890,25 @@
       <c r="K80">
         <v>0</v>
       </c>
-      <c r="L80" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>194</v>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>SDG Index Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>17_01_02_01_iil</t>
+        </is>
       </c>
       <c r="B81">
         <v>17</v>
       </c>
-      <c r="C81" t="s">
-        <v>195</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Porcentaje de ingresos que proviene de fuentes locales</t>
+        </is>
       </c>
       <c r="D81">
         <v>100</v>
@@ -4056,19 +3934,25 @@
       <c r="K81">
         <v>0</v>
       </c>
-      <c r="L81" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>196</v>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Atlas Municipal de los ODS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>17_18_01_02_ipc</t>
+        </is>
       </c>
       <c r="B82">
         <v>17</v>
       </c>
-      <c r="C82" t="s">
-        <v>197</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Inversión pública per cápita</t>
+        </is>
       </c>
       <c r="D82">
         <v>5000</v>
@@ -4094,12 +3978,13 @@
       <c r="K82">
         <v>0</v>
       </c>
-      <c r="L82" t="s">
-        <v>198</v>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Criterio de expertos (Taller externo)</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/umbrales_color_annexed_19-06-2026.xlsx
+++ b/umbrales_color_annexed_19-06-2026.xlsx
@@ -1,21 +1,630 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\sdsn\atlas_sdsn_paolo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FFAF0CB-779A-48F8-964C-B16BAAB26638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="198">
+  <si>
+    <t>indicator_code</t>
+  </si>
+  <si>
+    <t>ODS</t>
+  </si>
+  <si>
+    <t>Indicador</t>
+  </si>
+  <si>
+    <t>Green_max</t>
+  </si>
+  <si>
+    <t>Green_min</t>
+  </si>
+  <si>
+    <t>Yellow_max</t>
+  </si>
+  <si>
+    <t>Yellow_min</t>
+  </si>
+  <si>
+    <t>Orange_max</t>
+  </si>
+  <si>
+    <t>Orange_min</t>
+  </si>
+  <si>
+    <t>Red_max</t>
+  </si>
+  <si>
+    <t>Red_min</t>
+  </si>
+  <si>
+    <t>Criterio umbral verde</t>
+  </si>
+  <si>
+    <t>01_02_02_01_mpi</t>
+  </si>
+  <si>
+    <t>Índice de Pobreza Multidimensional</t>
+  </si>
+  <si>
+    <t>Meta 1.2  Para 2030, reducir al menos a la mitad la proporción de hombres, mujeres y niños y niñas de todas las edades que viven en la pobreza en todas sus dimensiones con arreglo a las definiciones nacionales.</t>
+  </si>
+  <si>
+    <t>01_04_01_02_eep</t>
+  </si>
+  <si>
+    <t>Tasa de Pobreza Enegética</t>
+  </si>
+  <si>
+    <t>Atlas Municipal de los ODS 2020</t>
+  </si>
+  <si>
+    <t>01_04_01_03_nbi</t>
+  </si>
+  <si>
+    <t>Necesidades Básicas Insatisfechas</t>
+  </si>
+  <si>
+    <t>01_04_02_04_ssb</t>
+  </si>
+  <si>
+    <t>Acceso a los 3 servicios básicos, 2024 (% de hogares)</t>
+  </si>
+  <si>
+    <t>02_02_02_01_smu</t>
+  </si>
+  <si>
+    <t>Obesidad en mujeres (15-49 años)</t>
+  </si>
+  <si>
+    <t>SDG Index Global</t>
+  </si>
+  <si>
+    <t>02_02_02_02_dcn</t>
+  </si>
+  <si>
+    <t>Desnutrición crónica niños &lt; 5 años</t>
+  </si>
+  <si>
+    <t>02_02_02_03_osn</t>
+  </si>
+  <si>
+    <t>Obesidad en niños &lt; 5 años</t>
+  </si>
+  <si>
+    <t>Plan sectorial de desarrollo integral para vivir bien - Sector Salud 2021-2025</t>
+  </si>
+  <si>
+    <t>02_02_03_04_pam</t>
+  </si>
+  <si>
+    <t>Prevalencia de anemia en mujeres (15-49 años)</t>
+  </si>
+  <si>
+    <t>Organización Mundial de la Salud (Plan on maternal, infant and young child nutrition)</t>
+  </si>
+  <si>
+    <t>02_03_01_05_pac</t>
+  </si>
+  <si>
+    <t>Producción agrícola per cápita</t>
+  </si>
+  <si>
+    <t>Promedio + desviación estandar</t>
+  </si>
+  <si>
+    <t>02_03_01_06_rpa</t>
+  </si>
+  <si>
+    <t>Rendimiento agrícola (Tm/Ha)</t>
+  </si>
+  <si>
+    <t>02_05_01_07_idp</t>
+  </si>
+  <si>
+    <t>Índice de diversificación productiva con base SIIP</t>
+  </si>
+  <si>
+    <t>03_01_02_01_cpp</t>
+  </si>
+  <si>
+    <t>Cobertura de partos atendidos por personal de salud calificado(%)</t>
+  </si>
+  <si>
+    <t>03_02_01_02_tmi</t>
+  </si>
+  <si>
+    <t>Tasa de mortalidad infantil (&lt; 1 año) (por 1,000 nacidos vivos)</t>
+  </si>
+  <si>
+    <t>03_02_01_03_tmn</t>
+  </si>
+  <si>
+    <t>Tasa de mortalidad en niños (&lt; 5 años) (por 1,000 nacidos vivos)</t>
+  </si>
+  <si>
+    <t>03_03_01_04_vih</t>
+  </si>
+  <si>
+    <t>Incidencia de VIH por 1.000.000 habitantes en el periodo 2011-2013 y 2022-2024</t>
+  </si>
+  <si>
+    <t>10% del promedio nacional del 2012</t>
+  </si>
+  <si>
+    <t>03_03_02_05_tub</t>
+  </si>
+  <si>
+    <t>Incidencia de Tuberculosis por 100.000 habitantes en el periodo 2011-2013 y 2022-2024</t>
+  </si>
+  <si>
+    <t>03_03_03_06_vec</t>
+  </si>
+  <si>
+    <t>Tasa de enfermedades por vectores (Chagas, Malaria, Dengue) en el periodo 2011-2013 y 2022-2024</t>
+  </si>
+  <si>
+    <t>Metas de los programas nacionales e internacionales</t>
+  </si>
+  <si>
+    <t>03_07_02_07_tfa</t>
+  </si>
+  <si>
+    <t>Paridez media en adolescentes (15 a 19 años)</t>
+  </si>
+  <si>
+    <t>Desviacion estandar de valores del 2012</t>
+  </si>
+  <si>
+    <t>04_01_02_01_asm</t>
+  </si>
+  <si>
+    <t>Tasa de abandono escolar de mujeres en secundaria (Abandono/Matriculación) (%)</t>
+  </si>
+  <si>
+    <t>04_01_02_02_ash</t>
+  </si>
+  <si>
+    <t>Tasa de abandono escolar de hombres en secundaria (Abandono/Matriculación) (%)</t>
+  </si>
+  <si>
+    <t>04_02_02_03_tam</t>
+  </si>
+  <si>
+    <t>Tasa de asistencia a un establecimiento educativo de niñas de 4 a 5 años de edad</t>
+  </si>
+  <si>
+    <t>04_02_02_04_tah</t>
+  </si>
+  <si>
+    <t>Tasa de asistencia a un establecimiento educativo de niños de 4 a 5 años de edad</t>
+  </si>
+  <si>
+    <t>04_03_02_05_aem</t>
+  </si>
+  <si>
+    <t>Promedio de años de educación mujeres (edad 25 a 35)</t>
+  </si>
+  <si>
+    <t>Criterio de expertos con base en el Panorama Social de América Latina 2019 de CEPAL (Comisión Económica para América Latina y el Caribe)</t>
+  </si>
+  <si>
+    <t>04_03_02_06_aeh</t>
+  </si>
+  <si>
+    <t>Promedio de años de educación hombres (edad 25 a 35)</t>
+  </si>
+  <si>
+    <t>04_03_04_07_esm</t>
+  </si>
+  <si>
+    <t>Porcentaje de población de 19 años o mas con nivel de educación superior alcanzado (mujeres)</t>
+  </si>
+  <si>
+    <t>04_03_04_08_esh</t>
+  </si>
+  <si>
+    <t>Porcentaje de población de 19 años o mas con nivel de educación superior alcanzado (hombres)</t>
+  </si>
+  <si>
+    <t>04_06_01_09_alf</t>
+  </si>
+  <si>
+    <t>Tasa de alfabetización de personas de 15 años o más (%)</t>
+  </si>
+  <si>
+    <t>04_10_01_10_pci</t>
+  </si>
+  <si>
+    <t>Profesores calificados en nivel inicial</t>
+  </si>
+  <si>
+    <t>04_10_01_11_pcs</t>
+  </si>
+  <si>
+    <t>Profesores calificados en nivel secundario</t>
+  </si>
+  <si>
+    <t>05_01_01_01_pga</t>
+  </si>
+  <si>
+    <t>Paridad de género en abandono escolar en secundaria</t>
+  </si>
+  <si>
+    <t>Paridad alcanzada</t>
+  </si>
+  <si>
+    <t>05_01_01_02_pgm</t>
+  </si>
+  <si>
+    <t>Paridad de género en el índice de pobreza multidimensional</t>
+  </si>
+  <si>
+    <t>05_01_01_03_pge</t>
+  </si>
+  <si>
+    <t>Índice de paridad de género para años de estudio de la población de 25 a 35 años (mujeres/hombres)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paridad alcanzada_x000D_
+</t>
+  </si>
+  <si>
+    <t>05_01_01_04_pgp</t>
+  </si>
+  <si>
+    <t>Paridad de género en la tasa global de participación (≥14 años)</t>
+  </si>
+  <si>
+    <t>05_04_01_05_phc</t>
+  </si>
+  <si>
+    <t>Paridad de género en labores del hogar o labores de cuidado (15-24 años)</t>
+  </si>
+  <si>
+    <t>05_05_01_06_acm</t>
+  </si>
+  <si>
+    <t>Porcentaje de concejales mujeres</t>
+  </si>
+  <si>
+    <t>06_01_01_01_cap</t>
+  </si>
+  <si>
+    <t>Cobertura de agua potable</t>
+  </si>
+  <si>
+    <t>06_02_01_02_cas</t>
+  </si>
+  <si>
+    <t>Cobertura de saneamiento</t>
+  </si>
+  <si>
+    <t>06_03_01_03_tar</t>
+  </si>
+  <si>
+    <t>Índice de tratamiento de agua residual</t>
+  </si>
+  <si>
+    <t>07_01_01_01_cep</t>
+  </si>
+  <si>
+    <t>Consumo de electricidad residencial per cápita</t>
+  </si>
+  <si>
+    <t>World Bank, 2025. An Evaluation of the World Bank Group's Support to Electricity Access in Sub-Saharan Africa, 2015-24</t>
+  </si>
+  <si>
+    <t>07_01_01_02_cae</t>
+  </si>
+  <si>
+    <t>Cobertura de energía eléctrica, (% de población)</t>
+  </si>
+  <si>
+    <t>07_01_01_03_mcc</t>
+  </si>
+  <si>
+    <t>Porcentaje de medidores eléctricos residenciales con consumo cero</t>
+  </si>
+  <si>
+    <t>07_01_02_04_elc</t>
+  </si>
+  <si>
+    <t>Energía limpia para cocinar</t>
+  </si>
+  <si>
+    <t>08_05_02_01_tgm</t>
+  </si>
+  <si>
+    <t>Tasa global de participación mujeres (≥ 14 años), (%)</t>
+  </si>
+  <si>
+    <t>Prom + desviación estandar</t>
+  </si>
+  <si>
+    <t>08_05_02_02_tgh</t>
+  </si>
+  <si>
+    <t>Tasa global de participación hombres (≥ 14 años), (%)</t>
+  </si>
+  <si>
+    <t>08_06_01_03_etm</t>
+  </si>
+  <si>
+    <t>Proporción de mujeres que no estudian, ni participan en el mercado laboral (15-24 años)(%)</t>
+  </si>
+  <si>
+    <t>08_06_01_04_eth</t>
+  </si>
+  <si>
+    <t>Propoción de hombres que no estudian, ni participan en el mercado laboral (15-24 años)</t>
+  </si>
+  <si>
+    <t>08_09_02_05_pot</t>
+  </si>
+  <si>
+    <t>Porcentaje de población ocupada de 14 o más años de edad en actividades económicas relacionadas con el turismo</t>
+  </si>
+  <si>
+    <t>Criterio nacional / meta sectorial de referencia del PSDI Turismo 2021–2025</t>
+  </si>
+  <si>
+    <t>08_09_02_06_pbt</t>
+  </si>
+  <si>
+    <t>Porcentaje del PIB que corresponde a turismo</t>
+  </si>
+  <si>
+    <t>08_10_02_07_dsb</t>
+  </si>
+  <si>
+    <t>Densidad de sucursales bancarias  por 100.000 habitantes</t>
+  </si>
+  <si>
+    <t>09_01_01_01_vpc</t>
+  </si>
+  <si>
+    <t>Cantidad de vias fundamentales que pasan dentro de un municipio</t>
+  </si>
+  <si>
+    <t>Promedio de los valores del 2012</t>
+  </si>
+  <si>
+    <t>09_08_01_02_ci</t>
+  </si>
+  <si>
+    <t>Porcentaje de hogares con acceso a internet (%)</t>
+  </si>
+  <si>
+    <t>Criterio de expertos con base en UIT(Unión Internacional de Telecomunicaciones)</t>
+  </si>
+  <si>
+    <t>09_08_01_03_drb</t>
+  </si>
+  <si>
+    <t>Densidad de radiobases</t>
+  </si>
+  <si>
+    <t>Maximo - promedio + Desv Estandar de valores del 2012</t>
+  </si>
+  <si>
+    <t>09_08_01_04_tfc</t>
+  </si>
+  <si>
+    <t>Porcentaje de hogares con cobertura de telefonía fija o celular</t>
+  </si>
+  <si>
+    <t>10_02_01_01_esp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porcentaje de la población de 3 años o mas, que no hablan español (como su lengua materna, primero o segundo idioma)
+</t>
+  </si>
+  <si>
+    <t>10_02_01_02_pel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brecha de pobreza multidimensional según autoidentificación indígena
+</t>
+  </si>
+  <si>
+    <t>10_02_01_03_mre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brecha de pobreza migrantes/no-migrantes
+</t>
+  </si>
+  <si>
+    <t>10_02_01_04_tpm</t>
+  </si>
+  <si>
+    <t>Brecha de pobreza multidimensional entre hogares con jefe adulto mayor y sin jefe adulto mayor</t>
+  </si>
+  <si>
+    <t>10_02_01_05_gip</t>
+  </si>
+  <si>
+    <t>Gini del Índice de Pobreza Multidimensional</t>
+  </si>
+  <si>
+    <t>10_04_02_06_gin</t>
+  </si>
+  <si>
+    <t>Coeﬁciente de Gini de años de educación</t>
+  </si>
+  <si>
+    <t>11_01_01_01_thm</t>
+  </si>
+  <si>
+    <t>Tasa de hacinamiento</t>
+  </si>
+  <si>
+    <t>11_01_01_02_ssb</t>
+  </si>
+  <si>
+    <t>Hogares que no tienen servicio sanitario, baño o letrina (%)</t>
+  </si>
+  <si>
+    <t>11_01_01_03_ava</t>
+  </si>
+  <si>
+    <t>Porcentaje de viviendas adecuadas</t>
+  </si>
+  <si>
+    <t>Prom + 3*desviación estandar</t>
+  </si>
+  <si>
+    <t>11_02_01_04_atc</t>
+  </si>
+  <si>
+    <t>Asientos disponibles en el transporte colectivo por cada mil habitantes</t>
+  </si>
+  <si>
+    <t>11_06_01_05_ipr</t>
+  </si>
+  <si>
+    <t>Inversión pública municipal en residuos sólidos per cápita</t>
+  </si>
+  <si>
+    <t>BID, 2023. Sostenibilidad financiera de la gestión de residuos sólidos en América Latina y el Caribe</t>
+  </si>
+  <si>
+    <t>11_06_01_06_srr</t>
+  </si>
+  <si>
+    <t>Porcentaje de población con recolección de residuos</t>
+  </si>
+  <si>
+    <t>Criterio de expertos</t>
+  </si>
+  <si>
+    <t>11_06_02_07_ica</t>
+  </si>
+  <si>
+    <t>Concentracion promedio de PM 2.5 en manzanos , 2010-2012 y 2021-2023</t>
+  </si>
+  <si>
+    <t>Criterios y metas de la OMS</t>
+  </si>
+  <si>
+    <t>13_01_01_01_fec</t>
+  </si>
+  <si>
+    <t>Porcentaje de familias afectadas por eventos climáticos</t>
+  </si>
+  <si>
+    <t>13_01_03_02_icc</t>
+  </si>
+  <si>
+    <t>Indice de Vulnerabilidad al Cambio Climatico</t>
+  </si>
+  <si>
+    <t>13_02_02_03_epb</t>
+  </si>
+  <si>
+    <t>Emisiones de CO2 por pérdida de bosque per cápita</t>
+  </si>
+  <si>
+    <t>13_02_02_04_ect</t>
+  </si>
+  <si>
+    <t>Emisiones de CO2 por transporte per cápita</t>
+  </si>
+  <si>
+    <t>13_02_02_05_eci</t>
+  </si>
+  <si>
+    <t>Emisiones totales de CO2 por degradación por incendios per cápita</t>
+  </si>
+  <si>
+    <t>15_01_02_01_sap</t>
+  </si>
+  <si>
+    <t>Porcentaje de superficie de áreas protegidas por municipio</t>
+  </si>
+  <si>
+    <t>15_02_01_02_tpb</t>
+  </si>
+  <si>
+    <t>Tasa promedio de pérdida de bosque</t>
+  </si>
+  <si>
+    <t>15_05_02_03_pbd</t>
+  </si>
+  <si>
+    <t>Índice de pérdida de biodiversidad por deforestación</t>
+  </si>
+  <si>
+    <t>15_05_02_04_pbi</t>
+  </si>
+  <si>
+    <t>16_01_01_01_thp</t>
+  </si>
+  <si>
+    <t>Tasa de Homicidios por 100.000 habitantes en el periodo 2017-2019 y 2022-2024</t>
+  </si>
+  <si>
+    <t>16_06_01_02_cep</t>
+  </si>
+  <si>
+    <t>Porcentaje de presupuesto total que ha sido ejecutado</t>
+  </si>
+  <si>
+    <t>Atlas Municipal de los ODS / Barja, 2025. Viabilidad Municipal en Bolivia</t>
+  </si>
+  <si>
+    <t>16_07_02_03_tcs</t>
+  </si>
+  <si>
+    <t>Cantidad de conflictos</t>
+  </si>
+  <si>
+    <t>Criterio de expertos con base en la Agenda 2030 para el Desarrollo Sostenible de ONU (Organización de las Naciones Unidas)</t>
+  </si>
+  <si>
+    <t>16_09_01_04_nic</t>
+  </si>
+  <si>
+    <t>Niños inscritos en el registro civil (&lt; 5 años)</t>
+  </si>
+  <si>
+    <t>17_01_02_01_iil</t>
+  </si>
+  <si>
+    <t>Porcentaje de ingresos que proviene de fuentes locales</t>
+  </si>
+  <si>
+    <t>17_18_01_02_ipc</t>
+  </si>
+  <si>
+    <t>Inversión pública per cápita</t>
+  </si>
+  <si>
+    <t>Criterio de expertos (Taller externo)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +672,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +724,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +758,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +793,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,94 +969,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L82"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>indicator_code</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ODS</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Indicador</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Green_max</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Green_min</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Yellow_max</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Yellow_min</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Orange_max</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Orange_min</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Red_max</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Red_min</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Criterio umbral verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>01_02_02_01_mpi</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Índice de Pobreza Multidimensional</t>
-        </is>
+      <c r="C2" t="s">
+        <v>13</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F2">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G2">
         <v>0.13</v>
@@ -454,25 +1045,19 @@
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Meta 1.2  Para 2030, reducir al menos a la mitad la proporción de hombres, mujeres y niños y niñas de todas las edades que viven en la pobreza en todas sus dimensiones con arreglo a las definiciones nacionales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01_04_01_02_eep</t>
-        </is>
+      <c r="L2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Tasa de Pobreza Enegética</t>
-        </is>
+      <c r="C3" t="s">
+        <v>16</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -498,25 +1083,19 @@
       <c r="K3">
         <v>100</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>01_04_01_03_nbi</t>
-        </is>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Necesidades Básicas Insatisfechas</t>
-        </is>
+      <c r="C4" t="s">
+        <v>19</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -542,25 +1121,19 @@
       <c r="K4">
         <v>100</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>01_04_02_04_ssb</t>
-        </is>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>20</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Acceso a los 3 servicios básicos, 2024 (% de hogares)</t>
-        </is>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -586,25 +1159,19 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>02_02_02_01_smu</t>
-        </is>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Obesidad en mujeres (15-49 años)</t>
-        </is>
+      <c r="C6" t="s">
+        <v>23</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -630,25 +1197,19 @@
       <c r="K6">
         <v>100</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>02_02_02_02_dcn</t>
-        </is>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Desnutrición crónica niños &lt; 5 años</t>
-        </is>
+      <c r="C7" t="s">
+        <v>26</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -674,25 +1235,19 @@
       <c r="K7">
         <v>100</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>02_02_02_03_osn</t>
-        </is>
+      <c r="L7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>27</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Obesidad en niños &lt; 5 años</t>
-        </is>
+      <c r="C8" t="s">
+        <v>28</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -718,25 +1273,19 @@
       <c r="K8">
         <v>100</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Plan sectorial de desarrollo integral para vivir bien - Sector Salud 2021-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>02_02_03_04_pam</t>
-        </is>
+      <c r="L8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>30</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Prevalencia de anemia en mujeres (15-49 años)</t>
-        </is>
+      <c r="C9" t="s">
+        <v>31</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -762,25 +1311,19 @@
       <c r="K9">
         <v>100</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Organización Mundial de la Salud (Plan on maternal, infant and young child nutrition)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>02_03_01_05_pac</t>
-        </is>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>33</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Producción agrícola per cápita</t>
-        </is>
+      <c r="C10" t="s">
+        <v>34</v>
       </c>
       <c r="D10">
         <v>999</v>
@@ -806,25 +1349,19 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Promedio + desviación estandar</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>02_03_01_06_rpa</t>
-        </is>
+      <c r="L10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>36</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rendimiento agrícola (Tm/Ha)</t>
-        </is>
+      <c r="C11" t="s">
+        <v>37</v>
       </c>
       <c r="D11">
         <v>999</v>
@@ -850,25 +1387,19 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>02_05_01_07_idp</t>
-        </is>
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>38</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Índice de diversificación productiva con base SIIP</t>
-        </is>
+      <c r="C12" t="s">
+        <v>39</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -894,25 +1425,19 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Promedio + desviación estandar</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>03_01_02_01_cpp</t>
-        </is>
+      <c r="L12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>40</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Cobertura de partos atendidos por personal de salud calificado(%)</t>
-        </is>
+      <c r="C13" t="s">
+        <v>41</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -938,25 +1463,19 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>03_02_01_02_tmi</t>
-        </is>
+      <c r="L13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>42</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tasa de mortalidad infantil (&lt; 1 año) (por 1,000 nacidos vivos)</t>
-        </is>
+      <c r="C14" t="s">
+        <v>43</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -982,25 +1501,19 @@
       <c r="K14">
         <v>400</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>03_02_01_03_tmn</t>
-        </is>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>44</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tasa de mortalidad en niños (&lt; 5 años) (por 1,000 nacidos vivos)</t>
-        </is>
+      <c r="C15" t="s">
+        <v>45</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1026,25 +1539,19 @@
       <c r="K15">
         <v>300</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>03_03_01_04_vih</t>
-        </is>
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>46</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Incidencia de VIH por 1.000.000 habitantes en el periodo 2011-2013 y 2022-2024</t>
-        </is>
+      <c r="C16" t="s">
+        <v>47</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1070,25 +1577,19 @@
       <c r="K16">
         <v>20000</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>10% del promedio nacional del 2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>03_03_02_05_tub</t>
-        </is>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>49</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Incidencia de Tuberculosis por 100.000 habitantes en el periodo 2011-2013 y 2022-2024</t>
-        </is>
+      <c r="C17" t="s">
+        <v>50</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1114,25 +1615,19 @@
       <c r="K17">
         <v>433.4</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>03_03_03_06_vec</t>
-        </is>
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>51</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tasa de enfermedades por vectores (Chagas, Malaria, Dengue) en el periodo 2011-2013 y 2022-2024</t>
-        </is>
+      <c r="C18" t="s">
+        <v>52</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1141,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1E-07</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="G18">
         <v>0.1</v>
@@ -1158,25 +1653,19 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Metas de los programas nacionales e internacionales</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>03_07_02_07_tfa</t>
-        </is>
+      <c r="L18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>54</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Paridez media en adolescentes (15 a 19 años)</t>
-        </is>
+      <c r="C19" t="s">
+        <v>55</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1202,25 +1691,19 @@
       <c r="K19">
         <v>1.17</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Desviacion estandar de valores del 2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>04_01_02_01_asm</t>
-        </is>
+      <c r="L19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>57</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tasa de abandono escolar de mujeres en secundaria (Abandono/Matriculación) (%)</t>
-        </is>
+      <c r="C20" t="s">
+        <v>58</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1246,25 +1729,19 @@
       <c r="K20">
         <v>100</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>04_01_02_02_ash</t>
-        </is>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>59</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tasa de abandono escolar de hombres en secundaria (Abandono/Matriculación) (%)</t>
-        </is>
+      <c r="C21" t="s">
+        <v>60</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1290,25 +1767,19 @@
       <c r="K21">
         <v>100</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>04_02_02_03_tam</t>
-        </is>
+      <c r="L21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>61</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tasa de asistencia a un establecimiento educativo de niñas de 4 a 5 años de edad</t>
-        </is>
+      <c r="C22" t="s">
+        <v>62</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -1334,25 +1805,19 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>04_02_02_04_tah</t>
-        </is>
+      <c r="L22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>63</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tasa de asistencia a un establecimiento educativo de niños de 4 a 5 años de edad</t>
-        </is>
+      <c r="C23" t="s">
+        <v>64</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -1378,25 +1843,19 @@
       <c r="K23">
         <v>18</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>04_03_02_05_aem</t>
-        </is>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>65</v>
       </c>
       <c r="B24">
         <v>4</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Promedio de años de educación mujeres (edad 25 a 35)</t>
-        </is>
+      <c r="C24" t="s">
+        <v>66</v>
       </c>
       <c r="D24">
         <v>20</v>
@@ -1422,25 +1881,19 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Criterio de expertos con base en el Panorama Social de América Latina 2019 de CEPAL (Comisión Económica para América Latina y el Caribe)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>04_03_02_06_aeh</t>
-        </is>
+      <c r="L24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>68</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Promedio de años de educación hombres (edad 25 a 35)</t>
-        </is>
+      <c r="C25" t="s">
+        <v>69</v>
       </c>
       <c r="D25">
         <v>20</v>
@@ -1466,25 +1919,19 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Criterio de expertos con base en el Panorama Social de América Latina 2019 de CEPAL (Comisión Económica para América Latina y el Caribe)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>04_03_04_07_esm</t>
-        </is>
+      <c r="L25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>70</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Porcentaje de población de 19 años o mas con nivel de educación superior alcanzado (mujeres)</t>
-        </is>
+      <c r="C26" t="s">
+        <v>71</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -1510,25 +1957,19 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>04_03_04_08_esh</t>
-        </is>
+      <c r="L26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>72</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Porcentaje de población de 19 años o mas con nivel de educación superior alcanzado (hombres)</t>
-        </is>
+      <c r="C27" t="s">
+        <v>73</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -1554,25 +1995,19 @@
       <c r="K27">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>04_06_01_09_alf</t>
-        </is>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>74</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Tasa de alfabetización de personas de 15 años o más (%)</t>
-        </is>
+      <c r="C28" t="s">
+        <v>75</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -1598,40 +2033,34 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>04_10_01_10_pci</t>
-        </is>
+      <c r="L28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>76</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Profesores calificados en nivel inicial</t>
-        </is>
+      <c r="C29" t="s">
+        <v>77</v>
       </c>
       <c r="D29">
         <v>100</v>
       </c>
       <c r="E29">
-        <v>96.90000000000001</v>
+        <v>96.9</v>
       </c>
       <c r="F29">
-        <v>96.90000000000001</v>
+        <v>96.9</v>
       </c>
       <c r="G29">
-        <v>69.59999999999999</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H29">
-        <v>69.59999999999999</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="I29">
         <v>42.3</v>
@@ -1642,40 +2071,34 @@
       <c r="K29">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>04_10_01_11_pcs</t>
-        </is>
+      <c r="L29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>78</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Profesores calificados en nivel secundario</t>
-        </is>
+      <c r="C30" t="s">
+        <v>79</v>
       </c>
       <c r="D30">
         <v>100</v>
       </c>
       <c r="E30">
-        <v>96.90000000000001</v>
+        <v>96.9</v>
       </c>
       <c r="F30">
-        <v>96.90000000000001</v>
+        <v>96.9</v>
       </c>
       <c r="G30">
-        <v>69.59999999999999</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H30">
-        <v>69.59999999999999</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="I30">
         <v>42.3</v>
@@ -1686,25 +2109,19 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>05_01_01_01_pga</t>
-        </is>
+      <c r="L30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>80</v>
       </c>
       <c r="B31">
         <v>5</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Paridad de género en abandono escolar en secundaria</t>
-        </is>
+      <c r="C31" t="s">
+        <v>81</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -1730,25 +2147,19 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Paridad alcanzada</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>05_01_01_02_pgm</t>
-        </is>
+      <c r="L31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>83</v>
       </c>
       <c r="B32">
         <v>5</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Paridad de género en el índice de pobreza multidimensional</t>
-        </is>
+      <c r="C32" t="s">
+        <v>84</v>
       </c>
       <c r="D32">
         <v>999</v>
@@ -1774,25 +2185,19 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Paridad alcanzada</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>05_01_01_03_pge</t>
-        </is>
+      <c r="L32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>85</v>
       </c>
       <c r="B33">
         <v>5</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Índice de paridad de género para años de estudio de la población de 25 a 35 años (mujeres/hombres)</t>
-        </is>
+      <c r="C33" t="s">
+        <v>86</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1818,26 +2223,19 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paridad alcanzada_x000D_
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>05_01_01_04_pgp</t>
-        </is>
+      <c r="L33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>88</v>
       </c>
       <c r="B34">
         <v>5</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Paridad de género en la tasa global de participación (≥14 años)</t>
-        </is>
+      <c r="C34" t="s">
+        <v>89</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -1863,25 +2261,19 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Paridad alcanzada</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>05_04_01_05_phc</t>
-        </is>
+      <c r="L34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>90</v>
       </c>
       <c r="B35">
         <v>5</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Paridad de género en labores del hogar o labores de cuidado (15-24 años)</t>
-        </is>
+      <c r="C35" t="s">
+        <v>91</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -1907,25 +2299,19 @@
       <c r="K35">
         <v>0</v>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Paridad alcanzada</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>05_05_01_06_acm</t>
-        </is>
+      <c r="L35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>92</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Porcentaje de concejales mujeres</t>
-        </is>
+      <c r="C36" t="s">
+        <v>93</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -1951,25 +2337,19 @@
       <c r="K36">
         <v>0</v>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>06_01_01_01_cap</t>
-        </is>
+      <c r="L36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>94</v>
       </c>
       <c r="B37">
         <v>6</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Cobertura de agua potable</t>
-        </is>
+      <c r="C37" t="s">
+        <v>95</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -1995,25 +2375,19 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>06_02_01_02_cas</t>
-        </is>
+      <c r="L37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>96</v>
       </c>
       <c r="B38">
         <v>6</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Cobertura de saneamiento</t>
-        </is>
+      <c r="C38" t="s">
+        <v>97</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -2039,25 +2413,19 @@
       <c r="K38">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>06_03_01_03_tar</t>
-        </is>
+      <c r="L38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>98</v>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Índice de tratamiento de agua residual</t>
-        </is>
+      <c r="C39" t="s">
+        <v>99</v>
       </c>
       <c r="D39">
         <v>500</v>
@@ -2083,25 +2451,19 @@
       <c r="K39">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>07_01_01_01_cep</t>
-        </is>
+      <c r="L39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>100</v>
       </c>
       <c r="B40">
         <v>7</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Consumo de electricidad residencial per cápita</t>
-        </is>
+      <c r="C40" t="s">
+        <v>101</v>
       </c>
       <c r="D40">
         <v>1700</v>
@@ -2127,25 +2489,19 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>World Bank, 2025. An Evaluation of the World Bank Group's Support to Electricity Access in Sub-Saharan Africa, 2015-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>07_01_01_02_cae</t>
-        </is>
+      <c r="L40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>103</v>
       </c>
       <c r="B41">
         <v>7</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Cobertura de energía eléctrica, (% de población)</t>
-        </is>
+      <c r="C41" t="s">
+        <v>104</v>
       </c>
       <c r="D41">
         <v>100</v>
@@ -2171,25 +2527,19 @@
       <c r="K41">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>07_01_01_03_mcc</t>
-        </is>
+      <c r="L41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>105</v>
       </c>
       <c r="B42">
         <v>7</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Porcentaje de medidores eléctricos residenciales con consumo cero</t>
-        </is>
+      <c r="C42" t="s">
+        <v>106</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2201,10 +2551,10 @@
         <v>4.5</v>
       </c>
       <c r="G42">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="H42">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I42">
         <v>24.9</v>
@@ -2215,25 +2565,19 @@
       <c r="K42">
         <v>100</v>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>07_01_02_04_elc</t>
-        </is>
+      <c r="L42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>107</v>
       </c>
       <c r="B43">
         <v>7</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Energía limpia para cocinar</t>
-        </is>
+      <c r="C43" t="s">
+        <v>108</v>
       </c>
       <c r="D43">
         <v>100</v>
@@ -2259,25 +2603,19 @@
       <c r="K43">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>08_05_02_01_tgm</t>
-        </is>
+      <c r="L43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>109</v>
       </c>
       <c r="B44">
         <v>8</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tasa global de participación mujeres (≥ 14 años), (%)</t>
-        </is>
+      <c r="C44" t="s">
+        <v>110</v>
       </c>
       <c r="D44">
         <v>100</v>
@@ -2303,25 +2641,19 @@
       <c r="K44">
         <v>0</v>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Prom + desviación estandar</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>08_05_02_02_tgh</t>
-        </is>
+      <c r="L44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>112</v>
       </c>
       <c r="B45">
         <v>8</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tasa global de participación hombres (≥ 14 años), (%)</t>
-        </is>
+      <c r="C45" t="s">
+        <v>113</v>
       </c>
       <c r="D45">
         <v>100</v>
@@ -2347,25 +2679,19 @@
       <c r="K45">
         <v>0</v>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Prom + desviación estandar</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>08_06_01_03_etm</t>
-        </is>
+      <c r="L45" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>114</v>
       </c>
       <c r="B46">
         <v>8</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Proporción de mujeres que no estudian, ni participan en el mercado laboral (15-24 años)(%)</t>
-        </is>
+      <c r="C46" t="s">
+        <v>115</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2391,25 +2717,19 @@
       <c r="K46">
         <v>100</v>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>08_06_01_04_eth</t>
-        </is>
+      <c r="L46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>116</v>
       </c>
       <c r="B47">
         <v>8</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Propoción de hombres que no estudian, ni participan en el mercado laboral (15-24 años)</t>
-        </is>
+      <c r="C47" t="s">
+        <v>117</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2435,25 +2755,19 @@
       <c r="K47">
         <v>100</v>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>08_09_02_05_pot</t>
-        </is>
+      <c r="L47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>118</v>
       </c>
       <c r="B48">
         <v>8</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Porcentaje de población ocupada de 14 o más años de edad en actividades económicas relacionadas con el turismo</t>
-        </is>
+      <c r="C48" t="s">
+        <v>119</v>
       </c>
       <c r="D48">
         <v>13</v>
@@ -2479,25 +2793,19 @@
       <c r="K48">
         <v>0</v>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Criterio nacional / meta sectorial de referencia del PSDI Turismo 2021–2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>08_09_02_06_pbt</t>
-        </is>
+      <c r="L48" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>121</v>
       </c>
       <c r="B49">
         <v>8</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Porcentaje del PIB que corresponde a turismo</t>
-        </is>
+      <c r="C49" t="s">
+        <v>122</v>
       </c>
       <c r="D49">
         <v>100</v>
@@ -2523,25 +2831,19 @@
       <c r="K49">
         <v>0</v>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Criterio nacional / meta sectorial de referencia del PSDI Turismo 2021–2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>08_10_02_07_dsb</t>
-        </is>
+      <c r="L49" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>123</v>
       </c>
       <c r="B50">
         <v>8</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Densidad de sucursales bancarias  por 100.000 habitantes</t>
-        </is>
+      <c r="C50" t="s">
+        <v>124</v>
       </c>
       <c r="D50">
         <v>225</v>
@@ -2567,25 +2869,19 @@
       <c r="K50">
         <v>0</v>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>09_01_01_01_vpc</t>
-        </is>
+      <c r="L50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>125</v>
       </c>
       <c r="B51">
         <v>9</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Cantidad de vias fundamentales que pasan dentro de un municipio</t>
-        </is>
+      <c r="C51" t="s">
+        <v>126</v>
       </c>
       <c r="D51">
         <v>6</v>
@@ -2603,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>1E-05</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -2611,25 +2907,19 @@
       <c r="K51">
         <v>0</v>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Promedio de los valores del 2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>09_08_01_02_ci</t>
-        </is>
+      <c r="L51" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>128</v>
       </c>
       <c r="B52">
         <v>9</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Porcentaje de hogares con acceso a internet (%)</t>
-        </is>
+      <c r="C52" t="s">
+        <v>129</v>
       </c>
       <c r="D52">
         <v>100</v>
@@ -2655,25 +2945,19 @@
       <c r="K52">
         <v>0</v>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Criterio de expertos con base en UIT(Unión Internacional de Telecomunicaciones)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>09_08_01_03_drb</t>
-        </is>
+      <c r="L52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>131</v>
       </c>
       <c r="B53">
         <v>9</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Densidad de radiobases</t>
-        </is>
+      <c r="C53" t="s">
+        <v>132</v>
       </c>
       <c r="D53">
         <v>6</v>
@@ -2699,25 +2983,19 @@
       <c r="K53">
         <v>0</v>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Maximo - promedio + Desv Estandar de valores del 2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>09_08_01_04_tfc</t>
-        </is>
+      <c r="L53" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>134</v>
       </c>
       <c r="B54">
         <v>9</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Porcentaje de hogares con cobertura de telefonía fija o celular</t>
-        </is>
+      <c r="C54" t="s">
+        <v>135</v>
       </c>
       <c r="D54">
         <v>100</v>
@@ -2743,26 +3021,19 @@
       <c r="K54">
         <v>0</v>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>10_02_01_01_esp</t>
-        </is>
+      <c r="L54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>136</v>
       </c>
       <c r="B55">
         <v>10</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Porcentaje de la población de 3 años o mas, que no hablan español (como su lengua materna, primero o segundo idioma)
-</t>
-        </is>
+      <c r="C55" t="s">
+        <v>137</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2788,26 +3059,19 @@
       <c r="K55">
         <v>100</v>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>10_02_01_02_pel</t>
-        </is>
+      <c r="L55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>138</v>
       </c>
       <c r="B56">
         <v>10</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brecha de pobreza multidimensional según autoidentificación indígena
-</t>
-        </is>
+      <c r="C56" t="s">
+        <v>139</v>
       </c>
       <c r="D56">
         <v>999</v>
@@ -2833,26 +3097,19 @@
       <c r="K56">
         <v>0</v>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Paridad alcanzada</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>10_02_01_03_mre</t>
-        </is>
+      <c r="L56" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>140</v>
       </c>
       <c r="B57">
         <v>10</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brecha de pobreza migrantes/no-migrantes
-</t>
-        </is>
+      <c r="C57" t="s">
+        <v>141</v>
       </c>
       <c r="D57">
         <v>999</v>
@@ -2878,25 +3135,19 @@
       <c r="K57">
         <v>0</v>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Paridad alcanzada</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>10_02_01_04_tpm</t>
-        </is>
+      <c r="L57" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>142</v>
       </c>
       <c r="B58">
         <v>10</v>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Brecha de pobreza multidimensional entre hogares con jefe adulto mayor y sin jefe adulto mayor</t>
-        </is>
+      <c r="C58" t="s">
+        <v>143</v>
       </c>
       <c r="D58">
         <v>999</v>
@@ -2922,25 +3173,19 @@
       <c r="K58">
         <v>0</v>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Paridad alcanzada</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>10_02_01_05_gip</t>
-        </is>
+      <c r="L58" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>144</v>
       </c>
       <c r="B59">
         <v>10</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Gini del Índice de Pobreza Multidimensional</t>
-        </is>
+      <c r="C59" t="s">
+        <v>145</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2966,25 +3211,19 @@
       <c r="K59">
         <v>1</v>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>10_04_02_06_gin</t>
-        </is>
+      <c r="L59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>146</v>
       </c>
       <c r="B60">
         <v>10</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Coeﬁciente de Gini de años de educación</t>
-        </is>
+      <c r="C60" t="s">
+        <v>147</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3010,25 +3249,19 @@
       <c r="K60">
         <v>1</v>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>11_01_01_01_thm</t>
-        </is>
+      <c r="L60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>148</v>
       </c>
       <c r="B61">
         <v>11</v>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Tasa de hacinamiento</t>
-        </is>
+      <c r="C61" t="s">
+        <v>149</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3054,25 +3287,19 @@
       <c r="K61">
         <v>100</v>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>11_01_01_02_ssb</t>
-        </is>
+      <c r="L61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>150</v>
       </c>
       <c r="B62">
         <v>11</v>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Hogares que no tienen servicio sanitario, baño o letrina (%)</t>
-        </is>
+      <c r="C62" t="s">
+        <v>151</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3098,25 +3325,19 @@
       <c r="K62">
         <v>100</v>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>11_01_01_03_ava</t>
-        </is>
+      <c r="L62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>152</v>
       </c>
       <c r="B63">
         <v>11</v>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Porcentaje de viviendas adecuadas</t>
-        </is>
+      <c r="C63" t="s">
+        <v>153</v>
       </c>
       <c r="D63">
         <v>100</v>
@@ -3142,25 +3363,19 @@
       <c r="K63">
         <v>0</v>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Prom + 3*desviación estandar</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>11_02_01_04_atc</t>
-        </is>
+      <c r="L63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>155</v>
       </c>
       <c r="B64">
         <v>11</v>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Asientos disponibles en el transporte colectivo por cada mil habitantes</t>
-        </is>
+      <c r="C64" t="s">
+        <v>156</v>
       </c>
       <c r="D64">
         <v>5400</v>
@@ -3186,25 +3401,19 @@
       <c r="K64">
         <v>0</v>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>11_06_01_05_ipr</t>
-        </is>
+      <c r="L64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>157</v>
       </c>
       <c r="B65">
         <v>11</v>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Inversión pública municipal en residuos sólidos per cápita</t>
-        </is>
+      <c r="C65" t="s">
+        <v>158</v>
       </c>
       <c r="D65">
         <v>999</v>
@@ -3230,25 +3439,19 @@
       <c r="K65">
         <v>0</v>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>BID, 2023. Sostenibilidad financiera de la gestión de residuos sólidos en América Latina y el Caribe</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>11_06_01_06_srr</t>
-        </is>
+      <c r="L65" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>160</v>
       </c>
       <c r="B66">
         <v>11</v>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Porcentaje de población con recolección de residuos</t>
-        </is>
+      <c r="C66" t="s">
+        <v>161</v>
       </c>
       <c r="D66">
         <v>100</v>
@@ -3274,25 +3477,19 @@
       <c r="K66">
         <v>0</v>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Criterio de expertos</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>11_06_02_07_ica</t>
-        </is>
+      <c r="L66" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>163</v>
       </c>
       <c r="B67">
         <v>11</v>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Concentracion promedio de PM 2.5 en manzanos , 2010-2012 y 2021-2023</t>
-        </is>
+      <c r="C67" t="s">
+        <v>164</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3318,25 +3515,19 @@
       <c r="K67">
         <v>32</v>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Criterios y metas de la OMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>13_01_01_01_fec</t>
-        </is>
+      <c r="L67" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>166</v>
       </c>
       <c r="B68">
         <v>13</v>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Porcentaje de familias afectadas por eventos climáticos</t>
-        </is>
+      <c r="C68" t="s">
+        <v>167</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3362,34 +3553,28 @@
       <c r="K68">
         <v>500</v>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Criterio de expertos</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>13_01_03_02_icc</t>
-        </is>
+      <c r="L68" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>168</v>
       </c>
       <c r="B69">
         <v>13</v>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Indice de Vulnerabilidad al Cambio Climatico</t>
-        </is>
+      <c r="C69" t="s">
+        <v>169</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="F69">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="G69">
         <v>1.55</v>
@@ -3406,25 +3591,19 @@
       <c r="K69">
         <v>3</v>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>13_02_02_03_epb</t>
-        </is>
+      <c r="L69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>170</v>
       </c>
       <c r="B70">
         <v>13</v>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Emisiones de CO2 por pérdida de bosque per cápita</t>
-        </is>
+      <c r="C70" t="s">
+        <v>171</v>
       </c>
       <c r="D70">
         <v>-20</v>
@@ -3450,25 +3629,19 @@
       <c r="K70">
         <v>450</v>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>13_02_02_04_ect</t>
-        </is>
+      <c r="L70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>172</v>
       </c>
       <c r="B71">
         <v>13</v>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Emisiones de CO2 por transporte per cápita</t>
-        </is>
+      <c r="C71" t="s">
+        <v>173</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3477,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>1E-07</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="G71">
         <v>0.2</v>
@@ -3494,25 +3667,19 @@
       <c r="K71">
         <v>99</v>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Promedio + desviación estandar</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>13_02_02_05_eci</t>
-        </is>
+      <c r="L71" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>174</v>
       </c>
       <c r="B72">
         <v>13</v>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Emisiones totales de CO2 por degradación por incendios per cápita</t>
-        </is>
+      <c r="C72" t="s">
+        <v>175</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3538,25 +3705,19 @@
       <c r="K72">
         <v>1300</v>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>15_01_02_01_sap</t>
-        </is>
+      <c r="L72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>176</v>
       </c>
       <c r="B73">
         <v>15</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Porcentaje de superficie de áreas protegidas por municipio</t>
-        </is>
+      <c r="C73" t="s">
+        <v>177</v>
       </c>
       <c r="D73">
         <v>100</v>
@@ -3582,25 +3743,19 @@
       <c r="K73">
         <v>0</v>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>15_02_01_02_tpb</t>
-        </is>
+      <c r="L73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>178</v>
       </c>
       <c r="B74">
         <v>15</v>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Tasa promedio de pérdida de bosque</t>
-        </is>
+      <c r="C74" t="s">
+        <v>179</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3626,25 +3781,19 @@
       <c r="K74">
         <v>100</v>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>15_05_02_03_pbd</t>
-        </is>
+      <c r="L74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>180</v>
       </c>
       <c r="B75">
         <v>15</v>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Índice de pérdida de biodiversidad por deforestación</t>
-        </is>
+      <c r="C75" t="s">
+        <v>181</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3670,25 +3819,19 @@
       <c r="K75">
         <v>5</v>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>15_05_02_04_pbi</t>
-        </is>
+      <c r="L75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>182</v>
       </c>
       <c r="B76">
         <v>15</v>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Índice de pérdida de biodiversidad por deforestación</t>
-        </is>
+      <c r="C76" t="s">
+        <v>181</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3714,25 +3857,19 @@
       <c r="K76">
         <v>62</v>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>16_01_01_01_thp</t>
-        </is>
+      <c r="L76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>183</v>
       </c>
       <c r="B77">
         <v>16</v>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Tasa de Homicidios por 100.000 habitantes en el periodo 2017-2019 y 2022-2024</t>
-        </is>
+      <c r="C77" t="s">
+        <v>184</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3758,25 +3895,19 @@
       <c r="K77">
         <v>60</v>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>16_06_01_02_cep</t>
-        </is>
+      <c r="L77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>185</v>
       </c>
       <c r="B78">
         <v>16</v>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Porcentaje de presupuesto total que ha sido ejecutado</t>
-        </is>
+      <c r="C78" t="s">
+        <v>186</v>
       </c>
       <c r="D78">
         <v>100</v>
@@ -3802,25 +3933,19 @@
       <c r="K78">
         <v>0</v>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS / Barja, 2025. Viabilidad Municipal en Bolivia</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>16_07_02_03_tcs</t>
-        </is>
+      <c r="L78" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>188</v>
       </c>
       <c r="B79">
         <v>16</v>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Cantidad de conflictos</t>
-        </is>
+      <c r="C79" t="s">
+        <v>189</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3829,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>1E-06</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -3846,25 +3971,19 @@
       <c r="K79">
         <v>1000</v>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Criterio de expertos con base en la Agenda 2030 para el Desarrollo Sostenible de ONU (Organización de las Naciones Unidas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>16_09_01_04_nic</t>
-        </is>
+      <c r="L79" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>191</v>
       </c>
       <c r="B80">
         <v>16</v>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Niños inscritos en el registro civil (&lt; 5 años)</t>
-        </is>
+      <c r="C80" t="s">
+        <v>192</v>
       </c>
       <c r="D80">
         <v>100</v>
@@ -3890,69 +4009,57 @@
       <c r="K80">
         <v>0</v>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>SDG Index Global</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>17_01_02_01_iil</t>
-        </is>
+      <c r="L80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>193</v>
       </c>
       <c r="B81">
         <v>17</v>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Porcentaje de ingresos que proviene de fuentes locales</t>
-        </is>
+      <c r="C81" t="s">
+        <v>194</v>
       </c>
       <c r="D81">
         <v>100</v>
       </c>
       <c r="E81">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F81">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G81">
+        <v>25</v>
+      </c>
+      <c r="H81">
+        <v>25</v>
+      </c>
+      <c r="I81">
         <v>10</v>
       </c>
-      <c r="H81">
+      <c r="J81">
         <v>10</v>
       </c>
-      <c r="I81">
-        <v>5</v>
-      </c>
-      <c r="J81">
-        <v>5</v>
-      </c>
       <c r="K81">
         <v>0</v>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Atlas Municipal de los ODS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>17_18_01_02_ipc</t>
-        </is>
+      <c r="L81" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>195</v>
       </c>
       <c r="B82">
         <v>17</v>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Inversión pública per cápita</t>
-        </is>
+      <c r="C82" t="s">
+        <v>196</v>
       </c>
       <c r="D82">
         <v>5000</v>
@@ -3978,10 +4085,8 @@
       <c r="K82">
         <v>0</v>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Criterio de expertos (Taller externo)</t>
-        </is>
+      <c r="L82" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
